--- a/output/yearly_surface_area_iteration_7_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_7_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.8449764524111</v>
+        <v>10.8449761377798</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907236072986</v>
+        <v>37.78907126440428</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.693154936927254</v>
+        <v>6.609125544989528</v>
       </c>
       <c r="C2" t="n">
-        <v>8.796459430051421</v>
+        <v>12.08629598698248</v>
       </c>
       <c r="D2" t="n">
-        <v>23.95758922673491</v>
+        <v>20.04434287760713</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.95893082733765</v>
+        <v>18.93300447639974</v>
       </c>
       <c r="C3" t="n">
-        <v>28.4854096387212</v>
+        <v>19.95402208881642</v>
       </c>
       <c r="D3" t="n">
-        <v>86.47233779005906</v>
+        <v>69.15921702566656</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.04566878267665</v>
+        <v>37.49687181600267</v>
       </c>
       <c r="C4" t="n">
-        <v>47.38797993628929</v>
+        <v>50.32340557198725</v>
       </c>
       <c r="D4" t="n">
-        <v>107.7811717107361</v>
+        <v>80.21369617548565</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.95208395560371</v>
+        <v>50.31456984264904</v>
       </c>
       <c r="C5" t="n">
-        <v>73.77833997414781</v>
+        <v>87.20373982972295</v>
       </c>
       <c r="D5" t="n">
-        <v>70.66129101316419</v>
+        <v>53.75068680751288</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.87430490278997</v>
+        <v>49.54978838104078</v>
       </c>
       <c r="C6" t="n">
-        <v>92.61906016634835</v>
+        <v>140.4782790006761</v>
       </c>
       <c r="D6" t="n">
-        <v>46.57116584635595</v>
+        <v>40.8151790563569</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.34443887993716</v>
+        <v>36.11162580531042</v>
       </c>
       <c r="C7" t="n">
-        <v>81.50567615427445</v>
+        <v>158.6396297815378</v>
       </c>
       <c r="D7" t="n">
-        <v>39.28561613314036</v>
+        <v>37.60879105428681</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.85384276525424</v>
+        <v>18.35868206941536</v>
       </c>
       <c r="C8" t="n">
-        <v>51.48775834922397</v>
+        <v>120.7500588838364</v>
       </c>
       <c r="D8" t="n">
-        <v>37.05115835827462</v>
+        <v>35.549084370777</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.432811868852599</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>32.8374972116473</v>
+        <v>62.01405723415825</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>33.45305302221006</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>28.60910984945629</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>28.42257778564941</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>26.27647730416588</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -965,7 +965,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
         <v>29.02537087605695</v>
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.711077779804445</v>
+        <v>7.644728038854258</v>
       </c>
       <c r="C21" t="n">
-        <v>96.38847224755555</v>
+        <v>92.69232747110787</v>
       </c>
       <c r="D21" t="n">
-        <v>8.67496250228</v>
+        <v>7.644728038854258</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.468735623282234</v>
+        <v>8.175994880967437</v>
       </c>
       <c r="C2" t="n">
-        <v>9.193085502567133</v>
+        <v>9.162651323735481</v>
       </c>
       <c r="D2" t="n">
-        <v>22.65873701401638</v>
+        <v>27.45653804467055</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.48278319077795</v>
+        <v>20.24854640009046</v>
       </c>
       <c r="C3" t="n">
-        <v>31.42083527441917</v>
+        <v>33.64940256305943</v>
       </c>
       <c r="D3" t="n">
-        <v>85.31878423756905</v>
+        <v>68.59471209572465</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.80317709972768</v>
+        <v>36.25888796094745</v>
       </c>
       <c r="C4" t="n">
-        <v>59.71676760622073</v>
+        <v>49.50659148205391</v>
       </c>
       <c r="D4" t="n">
-        <v>124.730064076853</v>
+        <v>92.29999216246813</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.20443417332415</v>
+        <v>52.76893910326607</v>
       </c>
       <c r="C5" t="n">
-        <v>79.84063204787186</v>
+        <v>88.84816723433634</v>
       </c>
       <c r="D5" t="n">
-        <v>90.7871189502238</v>
+        <v>67.54424205218056</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.17243740971151</v>
+        <v>57.80137783523521</v>
       </c>
       <c r="C6" t="n">
-        <v>105.0165701755771</v>
+        <v>140.2367690654314</v>
       </c>
       <c r="D6" t="n">
-        <v>56.11080828852221</v>
+        <v>46.69192081397831</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.3036885024443</v>
+        <v>46.8912155979404</v>
       </c>
       <c r="C7" t="n">
-        <v>107.3766916565864</v>
+        <v>178.7016441178214</v>
       </c>
       <c r="D7" t="n">
-        <v>43.5375654402333</v>
+        <v>40.60312155223958</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23.11524969649115</v>
+        <v>27.45457454926205</v>
       </c>
       <c r="C8" t="n">
-        <v>78.27474445959818</v>
+        <v>162.8915790886308</v>
       </c>
       <c r="D8" t="n">
-        <v>38.88702656521616</v>
+        <v>37.1346069131356</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.98281156740907</v>
+        <v>12.86874890726719</v>
       </c>
       <c r="C9" t="n">
-        <v>48.14687091167205</v>
+        <v>100.9531164276995</v>
       </c>
       <c r="D9" t="n">
-        <v>36.0546844384641</v>
+        <v>34.94530953266521</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.405903770210439</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>34.30717352490479</v>
+        <v>51.38958357879929</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>35.16129402759952</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>31.02617269731195</v>
+        <v>29.72437524148068</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>29.13827186204534</v>
+        <v>27.3171298706675</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>26.11939767148639</v>
+        <v>25.19753657719863</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1276,7 +1276,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>19.83915760741954</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.898812167338459</v>
+        <v>7.818377802634846</v>
       </c>
       <c r="C21" t="n">
-        <v>105.6466127381519</v>
+        <v>100.6616142089236</v>
       </c>
       <c r="D21" t="n">
-        <v>9.873515209173073</v>
+        <v>8.795675027964201</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.976119259928588</v>
+        <v>9.073312282649022</v>
       </c>
       <c r="C2" t="n">
-        <v>9.062513057902306</v>
+        <v>9.644689446520665</v>
       </c>
       <c r="D2" t="n">
-        <v>20.15528036818702</v>
+        <v>31.3314962333327</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.47434837206723</v>
+        <v>22.96798754085413</v>
       </c>
       <c r="C3" t="n">
-        <v>33.26652095840317</v>
+        <v>34.21390749300134</v>
       </c>
       <c r="D3" t="n">
-        <v>83.30129270534187</v>
+        <v>72.44316309637213</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.7949222074662</v>
+        <v>36.36098972218912</v>
       </c>
       <c r="C4" t="n">
-        <v>67.80833218462294</v>
+        <v>64.04332973883643</v>
       </c>
       <c r="D4" t="n">
-        <v>134.64669763745</v>
+        <v>100.9914045881651</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.92249265575607</v>
+        <v>53.55433726666352</v>
       </c>
       <c r="C5" t="n">
-        <v>92.84878912914211</v>
+        <v>88.74999246391167</v>
       </c>
       <c r="D5" t="n">
-        <v>110.9129468872834</v>
+        <v>81.31325360424208</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.6994970581718</v>
+        <v>62.95358978712248</v>
       </c>
       <c r="C6" t="n">
-        <v>115.2002391117292</v>
+        <v>141.2028088064103</v>
       </c>
       <c r="D6" t="n">
-        <v>68.14605339488386</v>
+        <v>54.21898046243861</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>50.84373185523806</v>
+        <v>55.63466065196249</v>
       </c>
       <c r="C7" t="n">
-        <v>126.8398398932794</v>
+        <v>188.5829347610656</v>
       </c>
       <c r="D7" t="n">
-        <v>48.92736033654828</v>
+        <v>44.13643153982385</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>31.87734795689393</v>
+        <v>36.80081269369168</v>
       </c>
       <c r="C8" t="n">
-        <v>107.5651872158018</v>
+        <v>194.1013386066369</v>
       </c>
       <c r="D8" t="n">
-        <v>41.0566889916016</v>
+        <v>38.80357801035517</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.19687362466387</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="C9" t="n">
-        <v>69.55780659359074</v>
+        <v>143.8859252821167</v>
       </c>
       <c r="D9" t="n">
-        <v>37.82968428774233</v>
+        <v>36.38749691020377</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.114144775599888</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
-        <v>44.69897297435728</v>
+        <v>78.43673283079892</v>
       </c>
       <c r="D10" t="n">
-        <v>36.01541453029424</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>35.7169632282032</v>
+        <v>43.35790561035613</v>
       </c>
       <c r="D11" t="n">
-        <v>37.49392657288993</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -1545,7 +1545,7 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.62976760897449</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
         <v>35.1485313074443</v>
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>31.73990327829938</v>
+        <v>29.39843500367074</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>28.27040689149115</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>25.44199175555609</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>19.25796296650543</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.071515080518612</v>
+        <v>7.976531285610562</v>
       </c>
       <c r="C21" t="n">
-        <v>114.0101505123254</v>
+        <v>107.6831723557426</v>
       </c>
       <c r="D21" t="n">
-        <v>11.09833323571309</v>
+        <v>9.970664107013203</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.028732725330414</v>
+        <v>8.324238784308704</v>
       </c>
       <c r="C2" t="n">
-        <v>6.017131679328701</v>
+        <v>6.634650985299944</v>
       </c>
       <c r="D2" t="n">
-        <v>16.60233542651781</v>
+        <v>25.76007801173206</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.314364554004</v>
+        <v>26.19793748782614</v>
       </c>
       <c r="C3" t="n">
-        <v>48.36089191119788</v>
+        <v>48.65050748395069</v>
       </c>
       <c r="D3" t="n">
-        <v>92.98623380773665</v>
+        <v>77.99985510240909</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.90832191507333</v>
+        <v>25.72964383290041</v>
       </c>
       <c r="C4" t="n">
-        <v>84.74446183058467</v>
+        <v>78.73322063748145</v>
       </c>
       <c r="D4" t="n">
-        <v>128.4950665226395</v>
+        <v>95.14607875707962</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.18936380039518</v>
+        <v>35.46563581591603</v>
       </c>
       <c r="C5" t="n">
-        <v>68.82051406770142</v>
+        <v>84.3566714874072</v>
       </c>
       <c r="D5" t="n">
-        <v>71.59395133219866</v>
+        <v>54.24156065963628</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.55729820530948</v>
+        <v>34.5359207399943</v>
       </c>
       <c r="C6" t="n">
-        <v>83.52218593879741</v>
+        <v>124.2166100275319</v>
       </c>
       <c r="D6" t="n">
-        <v>32.20132469929539</v>
+        <v>29.06169554111408</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.08008670558751</v>
+        <v>24.37385025333556</v>
       </c>
       <c r="C7" t="n">
-        <v>75.63678837828701</v>
+        <v>136.4815840966873</v>
       </c>
       <c r="D7" t="n">
-        <v>28.86534600026472</v>
+        <v>27.24840753137022</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.18210635137117</v>
+        <v>13.01797455831271</v>
       </c>
       <c r="C8" t="n">
-        <v>51.23741268464103</v>
+        <v>106.0631132283042</v>
       </c>
       <c r="D8" t="n">
-        <v>27.87181732356695</v>
+        <v>26.78698611037422</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>34.05780960802609</v>
+        <v>59.79530742256046</v>
       </c>
       <c r="D9" t="n">
-        <v>27.40156017323271</v>
+        <v>27.17968519207294</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>27.90126975469435</v>
+        <v>34.02246669067321</v>
       </c>
       <c r="D10" t="n">
-        <v>29.32480392585223</v>
+        <v>28.47068342315751</v>
       </c>
     </row>
     <row r="11">
@@ -1842,7 +1842,7 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
         <v>28.07602084605028</v>
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>24.58296251434014</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.58662746324986</v>
+        <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.37631247036279</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
-        <v>9.628981483252716</v>
+        <v>9.027170140549421</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.767366851822511</v>
+        <v>5.101161071266427</v>
       </c>
       <c r="C2" t="n">
-        <v>3.475386873033709</v>
+        <v>3.984913931537803</v>
       </c>
       <c r="D2" t="n">
-        <v>12.56244362354219</v>
+        <v>17.75490723130357</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.50366193447439</v>
+        <v>27.94053966286423</v>
       </c>
       <c r="C3" t="n">
-        <v>35.9663271450819</v>
+        <v>38.01817984695773</v>
       </c>
       <c r="D3" t="n">
-        <v>86.93375921105506</v>
+        <v>81.16108271008382</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.95258267722244</v>
+        <v>35.79943003535994</v>
       </c>
       <c r="C4" t="n">
-        <v>105.9050518479204</v>
+        <v>100.9020655470787</v>
       </c>
       <c r="D4" t="n">
-        <v>144.4484667166502</v>
+        <v>108.6617994014455</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.87091769132071</v>
+        <v>38.60722846950583</v>
       </c>
       <c r="C5" t="n">
-        <v>110.4466167277662</v>
+        <v>113.6863841517807</v>
       </c>
       <c r="D5" t="n">
-        <v>92.67698328089891</v>
+        <v>70.21950454625312</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.23907308041327</v>
+        <v>40.69442408873454</v>
       </c>
       <c r="C6" t="n">
-        <v>98.17378867697681</v>
+        <v>136.5336167250125</v>
       </c>
       <c r="D6" t="n">
-        <v>40.89568236810514</v>
+        <v>34.73717901936489</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.94224111636546</v>
+        <v>22.69702517448201</v>
       </c>
       <c r="C7" t="n">
-        <v>96.05812237432491</v>
+        <v>159.4181557110055</v>
       </c>
       <c r="D7" t="n">
-        <v>31.38058361854505</v>
+        <v>29.52409870981433</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.346238144429634</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>67.76022654711485</v>
+        <v>135.1866588747858</v>
       </c>
       <c r="D8" t="n">
-        <v>29.04009709162065</v>
+        <v>27.53802310412303</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>40.38124657107979</v>
+        <v>64.12186955517615</v>
       </c>
       <c r="D9" t="n">
-        <v>28.73281006019139</v>
+        <v>28.39999758845172</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>35.3036474447153</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.32480392585223</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>30.38607319414302</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.31989518733098</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>27.98864530037232</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>17.43093048890212</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>14.74977750860408</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>18.4372218857551</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>12.27773678931061</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
-        <v>8.025787482217675</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>63.19019098384595</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.381540004053514</v>
+        <v>4.94309969088269</v>
       </c>
       <c r="C2" t="n">
-        <v>5.263149442467151</v>
+        <v>6.433392705929348</v>
       </c>
       <c r="D2" t="n">
-        <v>15.05313754921634</v>
+        <v>23.03965512326415</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.74571164906685</v>
+        <v>22.61455836732528</v>
       </c>
       <c r="C3" t="n">
-        <v>23.59139733305085</v>
+        <v>26.37465207459056</v>
       </c>
       <c r="D3" t="n">
-        <v>77.47462008063705</v>
+        <v>76.73830930245194</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.56741878198821</v>
+        <v>44.28663893857362</v>
       </c>
       <c r="C4" t="n">
-        <v>98.41333511681302</v>
+        <v>97.81348726951822</v>
       </c>
       <c r="D4" t="n">
-        <v>154.1481340346087</v>
+        <v>122.0626555644144</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.60218086226435</v>
+        <v>45.45491870662732</v>
       </c>
       <c r="C5" t="n">
-        <v>152.8826612438346</v>
+        <v>148.3420781116931</v>
       </c>
       <c r="D5" t="n">
-        <v>120.0677442293849</v>
+        <v>89.38812847167209</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.51833139677587</v>
+        <v>46.00764266411829</v>
       </c>
       <c r="C6" t="n">
-        <v>135.4065703605371</v>
+        <v>158.5915241440298</v>
       </c>
       <c r="D6" t="n">
-        <v>57.39886127649402</v>
+        <v>45.8466360406218</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.72183090899544</v>
+        <v>32.99752208743954</v>
       </c>
       <c r="C7" t="n">
-        <v>119.4737868683156</v>
+        <v>177.7434583584765</v>
       </c>
       <c r="D7" t="n">
-        <v>35.33309987584271</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.01935721664445</v>
+        <v>15.60487975900305</v>
       </c>
       <c r="C8" t="n">
-        <v>96.21618375470864</v>
+        <v>171.3198831295896</v>
       </c>
       <c r="D8" t="n">
-        <v>31.04286240828414</v>
+        <v>28.95664853675967</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.434374453633594</v>
+        <v>6.767186925373262</v>
       </c>
       <c r="C9" t="n">
-        <v>60.57186985661969</v>
+        <v>108.3859282965521</v>
       </c>
       <c r="D9" t="n">
-        <v>29.50937249425062</v>
+        <v>29.28749751309084</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>38.72012945549421</v>
+        <v>51.24723016168351</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>29.60951076008381</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>34.11769621798515</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>29.852984190737</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>26.68684784454105</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.77239876353076</v>
+        <v>18.47158305540374</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>26.27647730416588</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>19.97365704290136</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.11106066376691</v>
+        <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>10.38885420633975</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>6.955682484588652</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.59475918232432</v>
+        <v>2.983531273206057</v>
       </c>
       <c r="C2" t="n">
-        <v>2.405281875404686</v>
+        <v>3.073852061996763</v>
       </c>
       <c r="D2" t="n">
-        <v>10.42419712369263</v>
+        <v>16.05648370295658</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.00449213236051</v>
+        <v>22.29549036344507</v>
       </c>
       <c r="C3" t="n">
-        <v>23.75338570425158</v>
+        <v>27.51347941151686</v>
       </c>
       <c r="D3" t="n">
-        <v>75.3638625165064</v>
+        <v>79.01596397630453</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.35343884019141</v>
+        <v>48.83016731382786</v>
       </c>
       <c r="C4" t="n">
-        <v>93.93362034233482</v>
+        <v>95.89907924623694</v>
       </c>
       <c r="D4" t="n">
-        <v>161.3973590827671</v>
+        <v>131.341153117251</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.90928796724435</v>
+        <v>47.93383165985053</v>
       </c>
       <c r="C5" t="n">
-        <v>181.5006068226291</v>
+        <v>178.8744317137689</v>
       </c>
       <c r="D5" t="n">
-        <v>130.0570271200962</v>
+        <v>94.71410976721104</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.55479493055324</v>
+        <v>38.76234460677682</v>
       </c>
       <c r="C6" t="n">
-        <v>168.6141864566855</v>
+        <v>196.3878290098278</v>
       </c>
       <c r="D6" t="n">
-        <v>56.19131160027045</v>
+        <v>45.28311285838414</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.282424543653592</v>
+        <v>10.30049691295753</v>
       </c>
       <c r="C7" t="n">
-        <v>126.1212005737707</v>
+        <v>199.841617433368</v>
       </c>
       <c r="D7" t="n">
-        <v>35.69241953559704</v>
+        <v>32.63820242768521</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.422773407631881</v>
+        <v>4.673119072214817</v>
       </c>
       <c r="C8" t="n">
-        <v>75.68783925890784</v>
+        <v>131.9321652352076</v>
       </c>
       <c r="D8" t="n">
-        <v>32.29459073119883</v>
+        <v>30.95941385342316</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>29.50937249425062</v>
+        <v>39.04999668412111</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>26.62008900065227</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>23.34596040698915</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>21.32356013624072</v>
+        <v>19.36890045708532</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>22.7451308119901</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.05550195525234</v>
+        <v>14.97067074205961</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.81278928812512</v>
+        <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.919578803709772</v>
+        <v>8.679631453246051</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.66664774891259</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.418445506187394</v>
+        <v>4.786020058203201</v>
       </c>
       <c r="C2" t="n">
-        <v>9.404161258980198</v>
+        <v>6.350925898772616</v>
       </c>
       <c r="D2" t="n">
-        <v>9.414960483726912</v>
+        <v>15.63924092865169</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.09437095279471</v>
+        <v>16.47863521578271</v>
       </c>
       <c r="C3" t="n">
-        <v>16.1742934274662</v>
+        <v>19.61531913085127</v>
       </c>
       <c r="D3" t="n">
-        <v>67.13681675491813</v>
+        <v>74.63246047684252</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.09069030835175</v>
+        <v>46.30314872309656</v>
       </c>
       <c r="C4" t="n">
-        <v>77.12511789792518</v>
+        <v>83.35332533366693</v>
       </c>
       <c r="D4" t="n">
-        <v>162.124834131614</v>
+        <v>138.7180053669616</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.56754195517523</v>
+        <v>58.56125055832225</v>
       </c>
       <c r="C5" t="n">
-        <v>179.0707812546182</v>
+        <v>179.3162181806799</v>
       </c>
       <c r="D5" t="n">
-        <v>153.7907778702629</v>
+        <v>114.5454133929966</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.90576188705487</v>
+        <v>48.62400029593603</v>
       </c>
       <c r="C6" t="n">
-        <v>224.4029814982147</v>
+        <v>236.5589815721987</v>
       </c>
       <c r="D6" t="n">
-        <v>78.61148392215486</v>
+        <v>59.4516957260741</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.13997331554657</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="C7" t="n">
-        <v>179.8394897070435</v>
+        <v>237.8696147573682</v>
       </c>
       <c r="D7" t="n">
-        <v>41.3816474817073</v>
+        <v>37.00992495469625</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.00829594999048</v>
+        <v>6.425538724295373</v>
       </c>
       <c r="C8" t="n">
-        <v>114.3245201595411</v>
+        <v>188.8440796503952</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>32.46148784092078</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>54.0265579124062</v>
+        <v>82.53749299143782</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>30.7483380970101</v>
+        <v>34.16482010778901</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0542014123786</v>
+        <v>24.62714116103124</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>24.87748682561417</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.45591614986479</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
-        <v>21.91359050649305</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.46681318560274</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>24.38563122578652</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>7.852999886270235</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>33.52766584773283</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.426880324898115</v>
+        <v>3.140610905885546</v>
       </c>
       <c r="C2" t="n">
-        <v>5.388813148610742</v>
+        <v>4.146902302738527</v>
       </c>
       <c r="D2" t="n">
-        <v>8.11316302789564</v>
+        <v>11.34703996568464</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.79355524466769</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="C3" t="n">
-        <v>25.99667920845554</v>
+        <v>22.0991408225957</v>
       </c>
       <c r="D3" t="n">
-        <v>61.07452468119408</v>
+        <v>70.99999397112933</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.55166976099125</v>
+        <v>41.7213321873767</v>
       </c>
       <c r="C4" t="n">
-        <v>62.92021036517808</v>
+        <v>70.97348678311465</v>
       </c>
       <c r="D4" t="n">
-        <v>160.4146296308161</v>
+        <v>144.5888566383575</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>65.06532909895736</v>
+        <v>64.30447462816609</v>
       </c>
       <c r="C5" t="n">
-        <v>170.7013820759142</v>
+        <v>175.7082953675729</v>
       </c>
       <c r="D5" t="n">
-        <v>170.2595956090031</v>
+        <v>128.2162501746335</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.80137783523521</v>
+        <v>56.63407981488576</v>
       </c>
       <c r="C6" t="n">
-        <v>255.7590214241536</v>
+        <v>263.6885976313551</v>
       </c>
       <c r="D6" t="n">
-        <v>94.18887474543901</v>
+        <v>71.56744414418399</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.54110721595601</v>
+        <v>19.70269467652924</v>
       </c>
       <c r="C7" t="n">
-        <v>231.3419742718311</v>
+        <v>278.5925095295258</v>
       </c>
       <c r="D7" t="n">
-        <v>47.07087542781757</v>
+        <v>40.90255460203486</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>5.17381040138069</v>
       </c>
       <c r="C8" t="n">
-        <v>148.2046334330985</v>
+        <v>232.6545709524091</v>
       </c>
       <c r="D8" t="n">
-        <v>36.21667280966483</v>
+        <v>33.46287049925253</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>65.12030697039516</v>
+        <v>92.41092965304799</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>31.8390597964283</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>32.17187226816798</v>
+        <v>34.30717352490479</v>
       </c>
       <c r="D10" t="n">
-        <v>25.76596849795754</v>
+        <v>25.0542014123786</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.52209415667683</v>
+        <v>22.56743447752142</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.00819813899924</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
         <v>16.3902779224005</v>
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>7.525096153051802</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.239186586937727</v>
+        <v>4.286310476741575</v>
       </c>
       <c r="C2" t="n">
-        <v>7.695920253590747</v>
+        <v>7.479935758656449</v>
       </c>
       <c r="D2" t="n">
-        <v>12.56440711895068</v>
+        <v>15.67654734141307</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.08884031946772</v>
+        <v>13.65611056607313</v>
       </c>
       <c r="C3" t="n">
-        <v>23.6404847182632</v>
+        <v>19.17844140246144</v>
       </c>
       <c r="D3" t="n">
-        <v>55.02695882303372</v>
+        <v>64.74135235655591</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.20859784385261</v>
+        <v>36.98636300979434</v>
       </c>
       <c r="C4" t="n">
-        <v>63.02231212641975</v>
+        <v>63.78807533573226</v>
       </c>
       <c r="D4" t="n">
-        <v>153.7524897097972</v>
+        <v>145.9544676949648</v>
       </c>
     </row>
     <row r="5">
@@ -3624,10 +3624,10 @@
         <v>63.54362015737481</v>
       </c>
       <c r="C5" t="n">
-        <v>146.1331457771377</v>
+        <v>156.2206034382737</v>
       </c>
       <c r="D5" t="n">
-        <v>184.9858111727053</v>
+        <v>144.439630987312</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>69.43410638285567</v>
+        <v>67.86429180376503</v>
       </c>
       <c r="C6" t="n">
-        <v>265.7414320809352</v>
+        <v>270.8533923769483</v>
       </c>
       <c r="D6" t="n">
-        <v>117.816596743547</v>
+        <v>87.94986808495052</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.06981156465531</v>
+        <v>35.45287309576081</v>
       </c>
       <c r="C7" t="n">
-        <v>288.2342537329338</v>
+        <v>320.8125695506599</v>
       </c>
       <c r="D7" t="n">
-        <v>58.38944471007905</v>
+        <v>48.14883440708056</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>10.09727513817844</v>
       </c>
       <c r="C8" t="n">
-        <v>212.7103663406351</v>
+        <v>289.6499339224577</v>
       </c>
       <c r="D8" t="n">
-        <v>39.22082078466007</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.884374755077128</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>108.9406157494515</v>
+        <v>163.4109236241773</v>
       </c>
       <c r="D9" t="n">
-        <v>34.16874709860598</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>48.82722207071512</v>
+        <v>59.36137493728339</v>
       </c>
       <c r="D10" t="n">
-        <v>27.3318560862312</v>
+        <v>26.05067533218912</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>28.07602084605028</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.26269177857742</v>
+        <v>19.30999559483051</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04880964777186</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
         <v>16.65044106402591</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.29148125717007</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>7.166758241001715</v>
+        <v>6.091744504851459</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.786020058203201</v>
+        <v>8.682576696358792</v>
       </c>
       <c r="C2" t="n">
-        <v>3.255475387282424</v>
+        <v>17.49376234197391</v>
       </c>
       <c r="D2" t="n">
-        <v>10.26515399560465</v>
+        <v>7.299294181075035</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.000220984178252</v>
+        <v>3.101340997715674</v>
       </c>
       <c r="C2" t="n">
-        <v>4.309872421643497</v>
+        <v>4.307908926235004</v>
       </c>
       <c r="D2" t="n">
-        <v>9.247081626300707</v>
+        <v>11.53848076801276</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.50670498857837</v>
+        <v>17.95125677215293</v>
       </c>
       <c r="C3" t="n">
-        <v>29.20208546282137</v>
+        <v>24.94620916491145</v>
       </c>
       <c r="D3" t="n">
-        <v>60.8192702780899</v>
+        <v>70.93618037035328</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.13272553318512</v>
+        <v>49.45554060143307</v>
       </c>
       <c r="C4" t="n">
-        <v>90.19414333685872</v>
+        <v>91.75119519579417</v>
       </c>
       <c r="D4" t="n">
-        <v>159.431900178865</v>
+        <v>148.3283336438336</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.45429681182157</v>
+        <v>39.39262663290327</v>
       </c>
       <c r="C5" t="n">
-        <v>222.2431365488717</v>
+        <v>229.9498560272092</v>
       </c>
       <c r="D5" t="n">
-        <v>170.1614208385784</v>
+        <v>130.2533766609456</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.98369550412208</v>
+        <v>22.01765576314322</v>
       </c>
       <c r="C6" t="n">
-        <v>244.5288094352744</v>
+        <v>264.3728757812151</v>
       </c>
       <c r="D6" t="n">
-        <v>91.17000055488006</v>
+        <v>70.68190771495337</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.827073535332318</v>
+        <v>6.647413705455153</v>
       </c>
       <c r="C7" t="n">
-        <v>149.5967516777205</v>
+        <v>203.6743604707475</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>31.14103717870882</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.002765316663493</v>
+        <v>1.835868206941535</v>
       </c>
       <c r="C8" t="n">
-        <v>80.27750977626168</v>
+        <v>120.4162646643925</v>
       </c>
       <c r="D8" t="n">
-        <v>25.11801501315464</v>
+        <v>24.11663235482289</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>37.27499683484289</v>
+        <v>45.26249615659493</v>
       </c>
       <c r="D9" t="n">
-        <v>20.85624822901923</v>
+        <v>19.85781081380023</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.63419332141022</v>
+        <v>21.92242623583128</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>19.07535789351553</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>17.05884810899257</v>
+        <v>15.45958109877452</v>
       </c>
       <c r="D11" t="n">
-        <v>16.70345544005523</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.28224461720434</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
         <v>13.4519070435898</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>10.14636252339079</v>
+        <v>9.365873098514571</v>
       </c>
       <c r="D13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>5.838453597155781</v>
+        <v>4.916592502868027</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.208572481656829</v>
+        <v>8.178940124080178</v>
       </c>
       <c r="C2" t="n">
-        <v>4.900884539600077</v>
+        <v>6.684720118216532</v>
       </c>
       <c r="D2" t="n">
-        <v>12.90507357232432</v>
+        <v>11.25082869066845</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.17090621599696</v>
+        <v>18.43231314723387</v>
       </c>
       <c r="C3" t="n">
-        <v>8.330129270534187</v>
+        <v>44.08047192068179</v>
       </c>
       <c r="D3" t="n">
-        <v>11.75642875835555</v>
+        <v>9.267698328089891</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>18.43525839034661</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4585,10 +4585,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>20.72076704583318</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>8.764061755811273</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>39.60468413702056</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>50.1084028247572</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.3988599945151</v>
+        <v>13.39625898792774</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14697291246141</v>
+        <v>70.13335587797465</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576336469942953</v>
+        <v>1.57603046916797</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.926810890537994</v>
+        <v>5.612651625179015</v>
       </c>
       <c r="C2" t="n">
-        <v>5.480115685105695</v>
+        <v>4.962734644967626</v>
       </c>
       <c r="D2" t="n">
-        <v>19.35319249381737</v>
+        <v>12.50648400440012</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.91060420565131</v>
+        <v>24.3767954964483</v>
       </c>
       <c r="C3" t="n">
-        <v>15.19254572321939</v>
+        <v>32.8100082759284</v>
       </c>
       <c r="D3" t="n">
-        <v>19.75276380944582</v>
+        <v>16.47863521578271</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.90761790480956</v>
+        <v>21.24992905842221</v>
       </c>
       <c r="C4" t="n">
-        <v>13.43914432343459</v>
+        <v>67.69346770322606</v>
       </c>
       <c r="D4" t="n">
-        <v>21.23716633826701</v>
+        <v>19.92260616228052</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>3.117048960983624</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.522330836388309</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.366053024963819</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.58368222013712</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.3139636433765</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
-        <v>25.36836067773758</v>
+        <v>25.20146356801562</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.96770980341364</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>25.84843530511426</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>40.04843409934012</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>49.68134257340984</v>
       </c>
     </row>
     <row r="11">
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4980,10 +4980,10 @@
         <v>5.203262832508096</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>26.53664044579129</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>44.74806035956962</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>44.86390658867074</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44486956742015</v>
+        <v>15.43380450622641</v>
       </c>
       <c r="C21" t="n">
-        <v>86.16611442876504</v>
+        <v>86.10438303473678</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251551487877926</v>
+        <v>3.249222001310822</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.384886157793755</v>
+        <v>5.943500601510189</v>
       </c>
       <c r="C2" t="n">
-        <v>4.91855599827652</v>
+        <v>5.729479601984385</v>
       </c>
       <c r="D2" t="n">
-        <v>23.80443658487241</v>
+        <v>15.64022267635594</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.19807635654638</v>
+        <v>21.57390580082366</v>
       </c>
       <c r="C3" t="n">
-        <v>18.90846078379357</v>
+        <v>24.74004214701962</v>
       </c>
       <c r="D3" t="n">
-        <v>30.65016332658542</v>
+        <v>22.65873701401638</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.623795007291</v>
+        <v>35.50588747179015</v>
       </c>
       <c r="C4" t="n">
-        <v>27.78444177788898</v>
+        <v>76.0913375653533</v>
       </c>
       <c r="D4" t="n">
-        <v>26.36777984066083</v>
+        <v>23.71313404837746</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.87285582453343</v>
+        <v>17.94143929511046</v>
       </c>
       <c r="C5" t="n">
-        <v>16.66516727958961</v>
+        <v>72.40389318820228</v>
       </c>
       <c r="D5" t="n">
-        <v>30.06602344255857</v>
+        <v>30.11511082777092</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.876741757621407</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.31700669748049</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.10573531908495</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.43373686329462</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>29.45733986592554</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>38.13598957146735</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.04687151455913</v>
       </c>
     </row>
     <row r="10">
@@ -5249,10 +5249,10 @@
         <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.60951076008381</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>49.39663573917827</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>49.04418831335365</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>29.65859814529614</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5305,10 +5305,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5347,7 +5347,7 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5361,10 +5361,10 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>31.56809743005619</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74367386884351</v>
+        <v>16.71733827665514</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1364105999454</v>
+        <v>101.1398965737636</v>
       </c>
       <c r="D21" t="n">
-        <v>5.023102160653054</v>
+        <v>4.179334569163784</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.788384464239194</v>
+        <v>6.08192702780899</v>
       </c>
       <c r="C2" t="n">
-        <v>4.82627171407732</v>
+        <v>4.797801030654163</v>
       </c>
       <c r="D2" t="n">
-        <v>34.13144068584461</v>
+        <v>27.49678970054466</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.79065105928395</v>
+        <v>21.04376204053038</v>
       </c>
       <c r="C3" t="n">
-        <v>19.01645303126072</v>
+        <v>23.29196428325558</v>
       </c>
       <c r="D3" t="n">
-        <v>41.92062697133881</v>
+        <v>29.50151851261665</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.84749461513903</v>
+        <v>38.44131310748811</v>
       </c>
       <c r="C4" t="n">
-        <v>38.90077103307561</v>
+        <v>68.29331555052087</v>
       </c>
       <c r="D4" t="n">
-        <v>35.03366682604742</v>
+        <v>29.40530723760046</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.41468274628643</v>
+        <v>35.02384934900497</v>
       </c>
       <c r="C5" t="n">
-        <v>35.71107274197773</v>
+        <v>108.5076650118787</v>
       </c>
       <c r="D5" t="n">
-        <v>32.91309178487433</v>
+        <v>31.857713002809</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.34467555964864</v>
+        <v>14.89311267342412</v>
       </c>
       <c r="C6" t="n">
-        <v>19.64280806657019</v>
+        <v>64.16113946334606</v>
       </c>
       <c r="D6" t="n">
-        <v>37.91705983342032</v>
+        <v>37.39378830705677</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.37951975538279</v>
       </c>
       <c r="D7" t="n">
-        <v>40.00425545264903</v>
+        <v>39.76470901281281</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.71045084717197</v>
+        <v>31.54355373745002</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>39.55461500410399</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>33.83593462686631</v>
+        <v>33.39218466454675</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>42.04530892977813</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.82722207071512</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>50.28806265463436</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>47.51560713784138</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="14">
@@ -5616,7 +5616,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.11412908006666</v>
       </c>
       <c r="D14" t="n">
         <v>45.7857676829585</v>
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>32.63820242768521</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07748704239723</v>
+        <v>18.0278172139468</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9340821337343</v>
+        <v>116.751578147465</v>
       </c>
       <c r="D21" t="n">
-        <v>6.886661730437042</v>
+        <v>6.009272404648932</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.257659866869169</v>
+        <v>6.470699118690727</v>
       </c>
       <c r="C2" t="n">
-        <v>4.431609136970102</v>
+        <v>4.047745784609599</v>
       </c>
       <c r="D2" t="n">
-        <v>41.07043345946106</v>
+        <v>34.64391298746145</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.33766445699867</v>
+        <v>18.52557917913731</v>
       </c>
       <c r="C3" t="n">
-        <v>17.7450897542611</v>
+        <v>19.38951715887451</v>
       </c>
       <c r="D3" t="n">
-        <v>55.06622873120359</v>
+        <v>40.40873550679871</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.90006702281185</v>
+        <v>28.77993394999525</v>
       </c>
       <c r="C4" t="n">
-        <v>36.74387132684537</v>
+        <v>51.91874559138832</v>
       </c>
       <c r="D4" t="n">
-        <v>41.1214843400819</v>
+        <v>31.702596865538</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.40209995258047</v>
+        <v>28.05344064885261</v>
       </c>
       <c r="C5" t="n">
-        <v>41.01251034491051</v>
+        <v>87.42463306317848</v>
       </c>
       <c r="D5" t="n">
-        <v>30.9495963763807</v>
+        <v>28.47068342315751</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.59247689174634</v>
+        <v>16.70443718775948</v>
       </c>
       <c r="C6" t="n">
-        <v>26.68684784454105</v>
+        <v>80.26180181299375</v>
       </c>
       <c r="D6" t="n">
-        <v>30.63151012020474</v>
+        <v>29.98748362621883</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.329908286355933</v>
+        <v>6.527640485537042</v>
       </c>
       <c r="C7" t="n">
-        <v>16.10949807898591</v>
+        <v>35.63253292563798</v>
       </c>
       <c r="D7" t="n">
-        <v>31.4404702285041</v>
+        <v>31.02126395879071</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>18.69247628885927</v>
       </c>
       <c r="D8" t="n">
-        <v>30.45872252425729</v>
+        <v>29.45733986592554</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>21.52187317249857</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.06830573313655</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>20.07968579496001</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>34.47308888692249</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5910,10 +5910,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.081305133003238</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
         <v>30.17892442854696</v>
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
         <v>29.80684204863741</v>
@@ -5941,10 +5941,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -5969,10 +5969,10 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>23.13881164139307</v>
       </c>
     </row>
     <row r="18">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6000,7 +6000,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.068465599995593</v>
+        <v>7.038683204421661</v>
       </c>
       <c r="C21" t="n">
-        <v>67.15042319995813</v>
+        <v>65.98765504145307</v>
       </c>
       <c r="D21" t="n">
-        <v>5.301349199996695</v>
+        <v>4.399177002763538</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.002405463764999</v>
+        <v>5.478152189697202</v>
       </c>
       <c r="C2" t="n">
-        <v>5.67253823513807</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="D2" t="n">
-        <v>31.85967649821749</v>
+        <v>25.09641656366122</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.45471341798229</v>
+        <v>20.930861054542</v>
       </c>
       <c r="C3" t="n">
-        <v>17.47510913559323</v>
+        <v>17.10695374650067</v>
       </c>
       <c r="D3" t="n">
-        <v>77.37153657169114</v>
+        <v>59.74425654193965</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.52842661125882</v>
+        <v>33.18307240354219</v>
       </c>
       <c r="C4" t="n">
-        <v>41.74685762768712</v>
+        <v>49.940523967331</v>
       </c>
       <c r="D4" t="n">
-        <v>61.41420938686347</v>
+        <v>45.52462279362884</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.09685853201772</v>
+        <v>37.03643214271093</v>
       </c>
       <c r="C5" t="n">
-        <v>57.80039608753097</v>
+        <v>92.75061435871743</v>
       </c>
       <c r="D5" t="n">
-        <v>39.71169463678348</v>
+        <v>33.55122779263475</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.65539086027615</v>
+        <v>28.57867567062465</v>
       </c>
       <c r="C6" t="n">
-        <v>49.71079500453725</v>
+        <v>114.435457650121</v>
       </c>
       <c r="D6" t="n">
-        <v>33.73088762251191</v>
+        <v>32.76484788153306</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.36038352291659</v>
+        <v>14.07335334037803</v>
       </c>
       <c r="C7" t="n">
-        <v>29.34443887993716</v>
+        <v>81.56556276423349</v>
       </c>
       <c r="D7" t="n">
-        <v>33.83593462686632</v>
+        <v>33.17718191731671</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>6.258641614573416</v>
       </c>
       <c r="C8" t="n">
-        <v>20.69524160552276</v>
+        <v>35.04839304161113</v>
       </c>
       <c r="D8" t="n">
-        <v>32.62838495064274</v>
+        <v>31.29320807286708</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>22.96406055003713</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.20008090968388</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>3.909319358310797</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>34.82848155585983</v>
       </c>
     </row>
     <row r="12">
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
         <v>32.97886888105885</v>
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>30.69925071179776</v>
       </c>
     </row>
     <row r="14">
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.20021977840412</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6294,7 +6294,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.29451014510453</v>
+        <v>7.253936640418012</v>
       </c>
       <c r="C21" t="n">
-        <v>77.50417029173563</v>
+        <v>75.25959264433689</v>
       </c>
       <c r="D21" t="n">
-        <v>6.382696376966464</v>
+        <v>5.440452480313509</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.548838024402973</v>
+        <v>5.394703634836223</v>
       </c>
       <c r="C2" t="n">
-        <v>8.88579847113788</v>
+        <v>4.75264063625881</v>
       </c>
       <c r="D2" t="n">
-        <v>26.90970457340507</v>
+        <v>24.41606540461818</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.7148765596077</v>
+        <v>19.78712497909446</v>
       </c>
       <c r="C3" t="n">
-        <v>20.32217747790898</v>
+        <v>21.89788254322511</v>
       </c>
       <c r="D3" t="n">
-        <v>84.90645020178539</v>
+        <v>65.52675051995337</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.16954891986099</v>
+        <v>37.52239725631309</v>
       </c>
       <c r="C4" t="n">
-        <v>42.99760420289756</v>
+        <v>45.42252103238718</v>
       </c>
       <c r="D4" t="n">
-        <v>85.77824216315656</v>
+        <v>63.72426173495622</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.22082078466008</v>
+        <v>43.81049130201392</v>
       </c>
       <c r="C5" t="n">
-        <v>68.55053344903355</v>
+        <v>92.57880851047423</v>
       </c>
       <c r="D5" t="n">
-        <v>53.55433726666352</v>
+        <v>42.36241343824987</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.12711278440013</v>
+        <v>40.29190752999335</v>
       </c>
       <c r="C6" t="n">
-        <v>73.78128521726055</v>
+        <v>132.669457761097</v>
       </c>
       <c r="D6" t="n">
-        <v>38.64158963915446</v>
+        <v>35.82397372796611</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.74450891718435</v>
+        <v>24.43373686329462</v>
       </c>
       <c r="C7" t="n">
-        <v>53.35896947351839</v>
+        <v>126.7200666733613</v>
       </c>
       <c r="D7" t="n">
-        <v>36.53083207502382</v>
+        <v>35.57264631567892</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>11.01520924164921</v>
       </c>
       <c r="C8" t="n">
-        <v>31.12631096314512</v>
+        <v>73.18438261307848</v>
       </c>
       <c r="D8" t="n">
-        <v>34.79804737702819</v>
+        <v>33.37942194439155</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>25.4046853427947</v>
+        <v>34.27968458918587</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>25.76596849795753</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>35.18387422479719</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>33.84673385161303</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6546,10 +6546,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>18.63357142660446</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.509252093477549</v>
+        <v>7.456323333545995</v>
       </c>
       <c r="C21" t="n">
-        <v>87.2950555866765</v>
+        <v>83.88363750239243</v>
       </c>
       <c r="D21" t="n">
-        <v>7.509252093477549</v>
+        <v>6.524282916852745</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_7_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_7_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.8449761377798</v>
+        <v>10.84497646374604</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907126440428</v>
+        <v>37.78907240022618</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.609125544989528</v>
+        <v>7.065638227464294</v>
       </c>
       <c r="C2" t="n">
-        <v>12.08629598698248</v>
+        <v>4.548437113775472</v>
       </c>
       <c r="D2" t="n">
-        <v>20.04434287760713</v>
+        <v>33.53257458625406</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.93300447639974</v>
+        <v>20.38108234016379</v>
       </c>
       <c r="C3" t="n">
-        <v>19.95402208881642</v>
+        <v>25.65306751196916</v>
       </c>
       <c r="D3" t="n">
-        <v>69.15921702566656</v>
+        <v>75.82037519898117</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.49687181600267</v>
+        <v>40.57268737340794</v>
       </c>
       <c r="C4" t="n">
-        <v>50.32340557198725</v>
+        <v>60.21451369227387</v>
       </c>
       <c r="D4" t="n">
-        <v>80.21369617548565</v>
+        <v>102.8675244509808</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.31456984264904</v>
+        <v>49.06284151973436</v>
       </c>
       <c r="C5" t="n">
-        <v>87.20373982972295</v>
+        <v>82.34408869370124</v>
       </c>
       <c r="D5" t="n">
-        <v>53.75068680751288</v>
+        <v>75.25096153051803</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.54978838104078</v>
+        <v>43.51203999992289</v>
       </c>
       <c r="C6" t="n">
-        <v>140.4782790006761</v>
+        <v>96.76498072138264</v>
       </c>
       <c r="D6" t="n">
-        <v>40.8151790563569</v>
+        <v>50.636583089642</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.11162580531042</v>
+        <v>30.00319158948677</v>
       </c>
       <c r="C7" t="n">
-        <v>158.6396297815378</v>
+        <v>83.48193428292328</v>
       </c>
       <c r="D7" t="n">
-        <v>37.60879105428681</v>
+        <v>39.88448223273092</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.35868206941536</v>
+        <v>15.35453409442011</v>
       </c>
       <c r="C8" t="n">
-        <v>120.7500588838364</v>
+        <v>51.57120690408495</v>
       </c>
       <c r="D8" t="n">
-        <v>35.549084370777</v>
+        <v>36.96770980341364</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.431249284071605</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>62.01405723415825</v>
+        <v>32.8374972116473</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>34.27968458918587</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>29.60951076008381</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>28.60910984945629</v>
+        <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>26.90381408717959</v>
+        <v>27.77167905773377</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>26.27647730416588</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.644728038854258</v>
+        <v>7.703134289529348</v>
       </c>
       <c r="C21" t="n">
-        <v>92.69232747110787</v>
+        <v>95.32628683292567</v>
       </c>
       <c r="D21" t="n">
-        <v>7.644728038854258</v>
+        <v>8.666026075720515</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.175994880967437</v>
+        <v>8.318348298083224</v>
       </c>
       <c r="C2" t="n">
-        <v>9.162651323735481</v>
+        <v>10.21606661039231</v>
       </c>
       <c r="D2" t="n">
-        <v>27.45653804467055</v>
+        <v>25.22698900832604</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.24854640009046</v>
+        <v>22.22185928562655</v>
       </c>
       <c r="C3" t="n">
-        <v>33.64940256305943</v>
+        <v>21.34319509032566</v>
       </c>
       <c r="D3" t="n">
-        <v>68.59471209572465</v>
+        <v>83.21293541195965</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.25888796094745</v>
+        <v>39.34746623850791</v>
       </c>
       <c r="C4" t="n">
-        <v>49.50659148205391</v>
+        <v>62.12892171555515</v>
       </c>
       <c r="D4" t="n">
-        <v>92.29999216246813</v>
+        <v>114.1242436278747</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.76893910326607</v>
+        <v>54.43791020048565</v>
       </c>
       <c r="C5" t="n">
-        <v>88.84816723433634</v>
+        <v>95.57313900842701</v>
       </c>
       <c r="D5" t="n">
-        <v>67.54424205218056</v>
+        <v>92.94696389956678</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.80137783523521</v>
+        <v>54.66174867705392</v>
       </c>
       <c r="C6" t="n">
-        <v>140.2367690654314</v>
+        <v>113.429166253268</v>
       </c>
       <c r="D6" t="n">
-        <v>46.69192081397831</v>
+        <v>60.61899374642356</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>46.8912155979404</v>
+        <v>40.18391528252619</v>
       </c>
       <c r="C7" t="n">
-        <v>178.7016441178214</v>
+        <v>109.8919292748667</v>
       </c>
       <c r="D7" t="n">
-        <v>40.60312155223958</v>
+        <v>45.03473068920969</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.45457454926205</v>
+        <v>23.36559536107409</v>
       </c>
       <c r="C8" t="n">
-        <v>162.8915790886308</v>
+        <v>80.02716411167874</v>
       </c>
       <c r="D8" t="n">
-        <v>37.1346069131356</v>
+        <v>38.88702656521616</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.86874890726719</v>
+        <v>11.42656152972862</v>
       </c>
       <c r="C9" t="n">
-        <v>100.9531164276995</v>
+        <v>47.48124596819272</v>
       </c>
       <c r="D9" t="n">
-        <v>34.94530953266521</v>
+        <v>36.0546844384641</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.690610604442014</v>
+        <v>6.548257187326225</v>
       </c>
       <c r="C10" t="n">
-        <v>51.38958357879929</v>
+        <v>34.73423377625215</v>
       </c>
       <c r="D10" t="n">
-        <v>35.16129402759952</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>32.16303653882975</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>37.13853390395258</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.72437524148068</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.3171298706675</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.818377802634846</v>
+        <v>7.888276006803159</v>
       </c>
       <c r="C21" t="n">
-        <v>100.6616142089236</v>
+        <v>104.5196570901419</v>
       </c>
       <c r="D21" t="n">
-        <v>8.795675027964201</v>
+        <v>9.860345008503948</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.073312282649022</v>
+        <v>8.941758090279949</v>
       </c>
       <c r="C2" t="n">
-        <v>9.644689446520665</v>
+        <v>6.403940274801944</v>
       </c>
       <c r="D2" t="n">
-        <v>31.3314962333327</v>
+        <v>32.55868086364122</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.96798754085413</v>
+        <v>24.52405765208533</v>
       </c>
       <c r="C3" t="n">
-        <v>34.21390749300134</v>
+        <v>30.06111470403734</v>
       </c>
       <c r="D3" t="n">
-        <v>72.44316309637213</v>
+        <v>83.24729658160828</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.36098972218912</v>
+        <v>39.97283952611313</v>
       </c>
       <c r="C4" t="n">
-        <v>64.04332973883643</v>
+        <v>57.84064774340508</v>
       </c>
       <c r="D4" t="n">
-        <v>100.9914045881651</v>
+        <v>126.3509295365645</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.55433726666352</v>
+        <v>56.18051237552373</v>
       </c>
       <c r="C5" t="n">
-        <v>88.74999246391167</v>
+        <v>102.9853341754904</v>
       </c>
       <c r="D5" t="n">
-        <v>81.31325360424208</v>
+        <v>107.4277425372073</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>62.95358978712248</v>
+        <v>63.31585468998956</v>
       </c>
       <c r="C6" t="n">
-        <v>141.2028088064103</v>
+        <v>129.5298286029157</v>
       </c>
       <c r="D6" t="n">
-        <v>54.21898046243861</v>
+        <v>73.01650375565229</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>55.63466065196249</v>
+        <v>50.783845245279</v>
       </c>
       <c r="C7" t="n">
-        <v>188.5829347610656</v>
+        <v>134.6250991879566</v>
       </c>
       <c r="D7" t="n">
-        <v>44.13643153982385</v>
+        <v>50.30475236560656</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.04424506661589</v>
       </c>
       <c r="C8" t="n">
-        <v>194.1013386066369</v>
+        <v>108.5665698741335</v>
       </c>
       <c r="D8" t="n">
-        <v>38.80357801035517</v>
+        <v>41.72427743048944</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18.74843590800133</v>
+        <v>16.64062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>143.8859252821167</v>
+        <v>70.44530651822986</v>
       </c>
       <c r="D9" t="n">
-        <v>36.38749691020377</v>
+        <v>37.27499683484289</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>78.43673283079892</v>
+        <v>44.12955930589413</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>36.01541453029424</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>5.508586368528851</v>
       </c>
       <c r="C11" t="n">
-        <v>43.35790561035613</v>
+        <v>35.7169632282032</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>37.49392657288993</v>
       </c>
     </row>
     <row r="12">
@@ -1545,7 +1545,7 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.1958351236974</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
         <v>35.1485313074443</v>
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.39843500367074</v>
+        <v>30.95941385342317</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>33.82120841130262</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>20.30548776693678</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>19.25796296650543</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.976531285610562</v>
+        <v>8.058712812782316</v>
       </c>
       <c r="C21" t="n">
-        <v>107.6831723557426</v>
+        <v>112.8219793789524</v>
       </c>
       <c r="D21" t="n">
-        <v>9.970664107013203</v>
+        <v>11.08073011757568</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.324238784308704</v>
+        <v>8.166177403924969</v>
       </c>
       <c r="C2" t="n">
-        <v>6.634650985299944</v>
+        <v>4.30300018771377</v>
       </c>
       <c r="D2" t="n">
-        <v>25.76007801173206</v>
+        <v>26.4257029552114</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.19793748782614</v>
+        <v>28.97628349084461</v>
       </c>
       <c r="C3" t="n">
-        <v>48.65050748395069</v>
+        <v>41.70955121492574</v>
       </c>
       <c r="D3" t="n">
-        <v>77.99985510240909</v>
+        <v>92.48063374004954</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.72964383290041</v>
+        <v>26.99315312826605</v>
       </c>
       <c r="C4" t="n">
-        <v>78.73322063748145</v>
+        <v>84.17013942360029</v>
       </c>
       <c r="D4" t="n">
-        <v>95.14607875707962</v>
+        <v>121.7691130008446</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.46563581591603</v>
+        <v>35.66198535676539</v>
       </c>
       <c r="C5" t="n">
-        <v>84.3566714874072</v>
+        <v>77.38626278725484</v>
       </c>
       <c r="D5" t="n">
-        <v>54.24156065963628</v>
+        <v>73.53290304808611</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.5359207399943</v>
+        <v>31.51704654943536</v>
       </c>
       <c r="C6" t="n">
-        <v>124.2166100275319</v>
+        <v>88.67439789068467</v>
       </c>
       <c r="D6" t="n">
-        <v>29.06169554111408</v>
+        <v>33.12711278440013</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.37385025333556</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="C7" t="n">
-        <v>136.4815840966873</v>
+        <v>76.29554108783661</v>
       </c>
       <c r="D7" t="n">
-        <v>27.24840753137022</v>
+        <v>29.34443887993716</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.01797455831271</v>
+        <v>11.51590057081509</v>
       </c>
       <c r="C8" t="n">
-        <v>106.0631132283042</v>
+        <v>51.90500112352886</v>
       </c>
       <c r="D8" t="n">
-        <v>26.78698611037422</v>
+        <v>27.45457454926205</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.323436963053704</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>59.79530742256046</v>
+        <v>33.61405964570653</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>27.40156017323271</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>34.02246669067321</v>
+        <v>27.90126975469435</v>
       </c>
       <c r="D10" t="n">
-        <v>28.47068342315751</v>
+        <v>29.32480392585223</v>
       </c>
     </row>
     <row r="11">
@@ -1842,7 +1842,7 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
         <v>28.07602084605028</v>
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>23.86628669023996</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>27.55471281509523</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>23.96838845148163</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>18.63357142660446</v>
       </c>
       <c r="D15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.57528845915541</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>16.58662746324986</v>
       </c>
       <c r="D18" t="n">
-        <v>13.37631247036279</v>
+        <v>13.9113649691773</v>
       </c>
     </row>
     <row r="19">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>75.31968386981528</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.101161071266427</v>
+        <v>4.871432108472673</v>
       </c>
       <c r="C2" t="n">
-        <v>3.984913931537803</v>
+        <v>2.141191742962294</v>
       </c>
       <c r="D2" t="n">
-        <v>17.75490723130357</v>
+        <v>19.16371518689774</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.94053966286423</v>
+        <v>29.43770491184061</v>
       </c>
       <c r="C3" t="n">
-        <v>38.01817984695773</v>
+        <v>29.13827186204533</v>
       </c>
       <c r="D3" t="n">
-        <v>81.16108271008382</v>
+        <v>92.54444734082558</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.79943003535994</v>
+        <v>39.47509344006</v>
       </c>
       <c r="C4" t="n">
-        <v>100.9020655470787</v>
+        <v>97.30297846330987</v>
       </c>
       <c r="D4" t="n">
-        <v>108.6617994014455</v>
+        <v>138.6286663258751</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.60722846950583</v>
+        <v>39.83441309981433</v>
       </c>
       <c r="C5" t="n">
-        <v>113.6863841517807</v>
+        <v>115.1590057081509</v>
       </c>
       <c r="D5" t="n">
-        <v>70.21950454625312</v>
+        <v>92.75061435871743</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.69442408873454</v>
+        <v>37.99756314516856</v>
       </c>
       <c r="C6" t="n">
-        <v>136.5336167250125</v>
+        <v>106.7473913781642</v>
       </c>
       <c r="D6" t="n">
-        <v>34.73717901936489</v>
+        <v>42.0629803884546</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.69702517448201</v>
+        <v>20.12190094624263</v>
       </c>
       <c r="C7" t="n">
-        <v>159.4181557110055</v>
+        <v>98.7530198224824</v>
       </c>
       <c r="D7" t="n">
-        <v>29.52409870981433</v>
+        <v>32.09922293805371</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>9.680032363873551</v>
       </c>
       <c r="C8" t="n">
-        <v>135.1866588747858</v>
+        <v>69.26230053461246</v>
       </c>
       <c r="D8" t="n">
-        <v>27.53802310412303</v>
+        <v>28.62285431731576</v>
       </c>
     </row>
     <row r="9">
@@ -2125,10 +2125,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>64.12186955517615</v>
+        <v>39.04999668412111</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>28.51093507903161</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>35.3036474447153</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>29.32480392585223</v>
+        <v>30.32127784566274</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>30.03068052520567</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>27.98864530037232</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>15.36435157146258</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>14.69185439405351</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.70599977254047</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>65.59743635465912</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.94309969088269</v>
+        <v>4.851797154387737</v>
       </c>
       <c r="C2" t="n">
-        <v>6.433392705929348</v>
+        <v>3.182826057168159</v>
       </c>
       <c r="D2" t="n">
-        <v>23.03965512326415</v>
+        <v>19.89609897426586</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.61455836732528</v>
+        <v>22.86981277042945</v>
       </c>
       <c r="C3" t="n">
-        <v>26.37465207459056</v>
+        <v>17.96598298771663</v>
       </c>
       <c r="D3" t="n">
-        <v>76.73830930245194</v>
+        <v>86.64414363830225</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.28663893857362</v>
+        <v>48.21755674637784</v>
       </c>
       <c r="C4" t="n">
-        <v>97.81348726951822</v>
+        <v>84.51473286779093</v>
       </c>
       <c r="D4" t="n">
-        <v>122.0626555644144</v>
+        <v>152.0295224888441</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.45491870662732</v>
+        <v>49.03829782712819</v>
       </c>
       <c r="C5" t="n">
-        <v>148.3420781116931</v>
+        <v>147.2866993296277</v>
       </c>
       <c r="D5" t="n">
-        <v>89.38812847167209</v>
+        <v>118.3005983617407</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.00764266411829</v>
+        <v>45.8466360406218</v>
       </c>
       <c r="C6" t="n">
-        <v>158.5915241440298</v>
+        <v>144.5436962439622</v>
       </c>
       <c r="D6" t="n">
-        <v>45.8466360406218</v>
+        <v>58.36490101747288</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.99752208743954</v>
+        <v>30.24273802932299</v>
       </c>
       <c r="C7" t="n">
-        <v>177.7434583584765</v>
+        <v>126.1212005737707</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>36.23139902522853</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.60487975900305</v>
+        <v>14.43659999094934</v>
       </c>
       <c r="C8" t="n">
-        <v>171.3198831295896</v>
+        <v>97.9686034067892</v>
       </c>
       <c r="D8" t="n">
-        <v>28.95664853675967</v>
+        <v>30.79251674370121</v>
       </c>
     </row>
     <row r="9">
@@ -2433,10 +2433,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.767186925373262</v>
+        <v>6.434374453633594</v>
       </c>
       <c r="C9" t="n">
-        <v>108.3859282965521</v>
+        <v>59.68436993198057</v>
       </c>
       <c r="D9" t="n">
         <v>29.28749751309084</v>
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>2.847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>51.24723016168351</v>
+        <v>38.43542262126263</v>
       </c>
       <c r="D10" t="n">
-        <v>29.60951076008381</v>
+        <v>30.89069151412589</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>34.11769621798515</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>29.07347651356504</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.47158305540374</v>
+        <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.66637001147211</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>15.11106066376691</v>
       </c>
       <c r="D17" t="n">
-        <v>10.38885420633975</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.7014351913845</v>
+        <v>35.50686921949439</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.983531273206057</v>
+        <v>2.869648539513427</v>
       </c>
       <c r="C2" t="n">
-        <v>3.073852061996763</v>
+        <v>1.48047553800419</v>
       </c>
       <c r="D2" t="n">
-        <v>16.05648370295658</v>
+        <v>13.72385115766616</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.29549036344507</v>
+        <v>22.38384765682728</v>
       </c>
       <c r="C3" t="n">
-        <v>27.51347941151686</v>
+        <v>16.6357148484622</v>
       </c>
       <c r="D3" t="n">
-        <v>79.01596397630453</v>
+        <v>86.00109889202059</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.83016731382786</v>
+        <v>53.15672944644354</v>
       </c>
       <c r="C4" t="n">
-        <v>95.89907924623694</v>
+        <v>78.60559343592936</v>
       </c>
       <c r="D4" t="n">
-        <v>131.341153117251</v>
+        <v>161.7291898068026</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.93383165985053</v>
+        <v>50.90361846519713</v>
       </c>
       <c r="C5" t="n">
-        <v>178.8744317137689</v>
+        <v>170.824100538945</v>
       </c>
       <c r="D5" t="n">
-        <v>94.71410976721104</v>
+        <v>128.2653375598458</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.76234460677682</v>
+        <v>37.83655652167208</v>
       </c>
       <c r="C6" t="n">
-        <v>196.3878290098278</v>
+        <v>177.9525706194811</v>
       </c>
       <c r="D6" t="n">
-        <v>45.28311285838414</v>
+        <v>57.19760299712343</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.30049691295753</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>199.841617433368</v>
+        <v>131.3912222501676</v>
       </c>
       <c r="D7" t="n">
-        <v>32.63820242768521</v>
+        <v>36.29128563518759</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.673119072214817</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>131.9321652352076</v>
+        <v>75.60439070404686</v>
       </c>
       <c r="D8" t="n">
-        <v>30.95941385342316</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>39.04999668412111</v>
+        <v>29.28749751309084</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>26.1930287493049</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34596040698915</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>19.36890045708532</v>
+        <v>21.14586380177204</v>
       </c>
       <c r="D11" t="n">
-        <v>22.7451308119901</v>
+        <v>23.27821981539612</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.97067074205961</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.82875929330033</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.90016483380309</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>12.81278928812512</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>9.506263020221864</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>30.22212132753381</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.89283493598363</v>
+        <v>30.49799243242716</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.786020058203201</v>
+        <v>4.316744655573225</v>
       </c>
       <c r="C2" t="n">
-        <v>6.350925898772616</v>
+        <v>2.521128104505809</v>
       </c>
       <c r="D2" t="n">
-        <v>15.63924092865169</v>
+        <v>11.22137625954104</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.47863521578271</v>
+        <v>16.26265072084841</v>
       </c>
       <c r="C3" t="n">
-        <v>19.61531913085127</v>
+        <v>10.90230825566083</v>
       </c>
       <c r="D3" t="n">
-        <v>74.63246047684252</v>
+        <v>77.8575016852933</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.30314872309656</v>
+        <v>48.35794666808514</v>
       </c>
       <c r="C4" t="n">
-        <v>83.35332533366693</v>
+        <v>60.40595449460199</v>
       </c>
       <c r="D4" t="n">
-        <v>138.7180053669616</v>
+        <v>166.898091469662</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.56125055832225</v>
+        <v>63.71542600561801</v>
       </c>
       <c r="C5" t="n">
-        <v>179.3162181806799</v>
+        <v>159.8285262513808</v>
       </c>
       <c r="D5" t="n">
-        <v>114.5454133929966</v>
+        <v>152.4163310843173</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.62400029593603</v>
+        <v>50.59633143376788</v>
       </c>
       <c r="C6" t="n">
-        <v>236.5589815721987</v>
+        <v>222.148888769264</v>
       </c>
       <c r="D6" t="n">
-        <v>59.4516957260741</v>
+        <v>79.05425213677017</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.85861263505523</v>
+        <v>21.37951975538279</v>
       </c>
       <c r="C7" t="n">
-        <v>237.8696147573682</v>
+        <v>188.7625945909427</v>
       </c>
       <c r="D7" t="n">
-        <v>37.00992495469625</v>
+        <v>42.10028680121597</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.425538724295373</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>188.8440796503952</v>
+        <v>117.0783224699534</v>
       </c>
       <c r="D8" t="n">
-        <v>32.46148784092078</v>
+        <v>34.13045893814036</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>82.53749299143782</v>
+        <v>53.80468293124643</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>33.28124717396686</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>34.16482010778901</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.08946221427348</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.44249047717483</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>24.38563122578652</v>
       </c>
       <c r="D16" t="n">
-        <v>7.852999886270235</v>
+        <v>8.266315669758143</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>34.94432778496098</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.140610905885546</v>
+        <v>3.006111470403733</v>
       </c>
       <c r="C2" t="n">
-        <v>4.146902302738527</v>
+        <v>2.109775816426395</v>
       </c>
       <c r="D2" t="n">
-        <v>11.34703996568464</v>
+        <v>8.198575078165113</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.52772260099505</v>
+        <v>15.80613803837365</v>
       </c>
       <c r="C3" t="n">
-        <v>22.0991408225957</v>
+        <v>10.49979169691964</v>
       </c>
       <c r="D3" t="n">
-        <v>70.99999397112933</v>
+        <v>71.0098114481718</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.7213321873767</v>
+        <v>42.83168884087984</v>
       </c>
       <c r="C4" t="n">
-        <v>70.97348678311465</v>
+        <v>47.33692905566846</v>
       </c>
       <c r="D4" t="n">
-        <v>144.5888566383575</v>
+        <v>168.1998889254933</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>64.30447462816609</v>
+        <v>69.63045592370504</v>
       </c>
       <c r="C5" t="n">
-        <v>175.7082953675729</v>
+        <v>146.2804079327748</v>
       </c>
       <c r="D5" t="n">
-        <v>128.2162501746335</v>
+        <v>170.1123334533661</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.63407981488576</v>
+        <v>60.25672884355649</v>
       </c>
       <c r="C6" t="n">
-        <v>263.6885976313551</v>
+        <v>244.1262928765332</v>
       </c>
       <c r="D6" t="n">
-        <v>71.56744414418399</v>
+        <v>94.3901330248096</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.70269467652924</v>
+        <v>20.78065365579224</v>
       </c>
       <c r="C7" t="n">
-        <v>278.5925095295258</v>
+        <v>237.7498415374501</v>
       </c>
       <c r="D7" t="n">
-        <v>40.90255460203486</v>
+        <v>47.78951474732623</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.17381040138069</v>
+        <v>5.006913291658733</v>
       </c>
       <c r="C8" t="n">
-        <v>232.6545709524091</v>
+        <v>152.7943039504523</v>
       </c>
       <c r="D8" t="n">
-        <v>33.46287049925253</v>
+        <v>36.13322425480386</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>92.41092965304799</v>
+        <v>65.12030697039516</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>34.30717352490479</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0542014123786</v>
+        <v>25.90832191507333</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.56743447752142</v>
+        <v>24.16670148773948</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.48943444052943</v>
+        <v>18.00819813899924</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>11.96750451476862</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.67690719431156</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.808420328951629</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.286310476741575</v>
+        <v>4.656429361242622</v>
       </c>
       <c r="C2" t="n">
-        <v>7.479935758656449</v>
+        <v>3.998658399397259</v>
       </c>
       <c r="D2" t="n">
-        <v>15.67654734141307</v>
+        <v>18.52067044061608</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.65611056607313</v>
+        <v>13.05233572796134</v>
       </c>
       <c r="C3" t="n">
-        <v>19.17844140246144</v>
+        <v>9.321694451823465</v>
       </c>
       <c r="D3" t="n">
-        <v>64.74135235655591</v>
+        <v>62.50787632939441</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.98636300979434</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="C4" t="n">
-        <v>63.78807533573226</v>
+        <v>37.49687181600267</v>
       </c>
       <c r="D4" t="n">
-        <v>145.9544676949648</v>
+        <v>165.609056733986</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>63.54362015737481</v>
+        <v>67.66696051521141</v>
       </c>
       <c r="C5" t="n">
-        <v>156.2206034382737</v>
+        <v>119.8959383811417</v>
       </c>
       <c r="D5" t="n">
-        <v>144.439630987312</v>
+        <v>187.0229376590174</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>67.86429180376503</v>
+        <v>73.78128521726055</v>
       </c>
       <c r="C6" t="n">
-        <v>270.8533923769483</v>
+        <v>240.2621339126177</v>
       </c>
       <c r="D6" t="n">
-        <v>87.94986808495052</v>
+        <v>117.9373517111694</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.45287309576081</v>
+        <v>38.86640986342697</v>
       </c>
       <c r="C7" t="n">
-        <v>320.8125695506599</v>
+        <v>289.1325528823196</v>
       </c>
       <c r="D7" t="n">
-        <v>48.14883440708056</v>
+        <v>59.04819741962866</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.09727513817844</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>289.6499339224577</v>
+        <v>217.38348541285</v>
       </c>
       <c r="D8" t="n">
-        <v>35.63253292563798</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.662499773917349</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>163.4109236241773</v>
+        <v>113.0453029009074</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>34.16874709860598</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>59.36137493728339</v>
+        <v>48.25780840225197</v>
       </c>
       <c r="D10" t="n">
-        <v>26.05067533218912</v>
+        <v>27.47420950334699</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.07602084605028</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.30999559483051</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.91060420565131</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.98419422574081</v>
       </c>
     </row>
     <row r="15">
@@ -3767,7 +3767,7 @@
         <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>6.091744504851459</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.69215749368978</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.682576696358792</v>
+        <v>5.724570863463152</v>
       </c>
       <c r="C2" t="n">
-        <v>17.49376234197391</v>
+        <v>3.514656781203581</v>
       </c>
       <c r="D2" t="n">
-        <v>7.299294181075035</v>
+        <v>12.57422459599315</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.101340997715674</v>
+        <v>3.297690538565036</v>
       </c>
       <c r="C2" t="n">
-        <v>4.307908926235004</v>
+        <v>2.20696883914683</v>
       </c>
       <c r="D2" t="n">
-        <v>11.53848076801276</v>
+        <v>13.63058512576272</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.95125677215293</v>
+        <v>17.68127615348505</v>
       </c>
       <c r="C3" t="n">
-        <v>24.94620916491145</v>
+        <v>12.7430852011236</v>
       </c>
       <c r="D3" t="n">
-        <v>70.93618037035328</v>
+        <v>69.60100349257762</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.45554060143307</v>
+        <v>51.20403326269664</v>
       </c>
       <c r="C4" t="n">
-        <v>91.75119519579417</v>
+        <v>57.5726306201457</v>
       </c>
       <c r="D4" t="n">
-        <v>148.3283336438336</v>
+        <v>171.8500268898829</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.39262663290327</v>
+        <v>44.05592822807562</v>
       </c>
       <c r="C5" t="n">
-        <v>229.9498560272092</v>
+        <v>191.3917149429157</v>
       </c>
       <c r="D5" t="n">
-        <v>130.2533766609456</v>
+        <v>171.683129780161</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.01765576314322</v>
+        <v>24.11074186859742</v>
       </c>
       <c r="C6" t="n">
-        <v>264.3728757812151</v>
+        <v>242.2344650504495</v>
       </c>
       <c r="D6" t="n">
-        <v>70.68190771495337</v>
+        <v>91.21025221075418</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.647413705455153</v>
+        <v>7.126506585127596</v>
       </c>
       <c r="C7" t="n">
-        <v>203.6743604707475</v>
+        <v>152.8306286155095</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.835868206941535</v>
+        <v>2.002765316663493</v>
       </c>
       <c r="C8" t="n">
-        <v>120.4162646643925</v>
+        <v>83.28165775125692</v>
       </c>
       <c r="D8" t="n">
-        <v>24.11663235482289</v>
+        <v>25.11801501315464</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>45.26249615659493</v>
+        <v>36.83124687252333</v>
       </c>
       <c r="D9" t="n">
-        <v>19.85781081380023</v>
+        <v>20.96718571959912</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.92242623583128</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D10" t="n">
-        <v>19.07535789351553</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.45958109877452</v>
+        <v>16.8811517745239</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -4375,7 +4375,7 @@
         <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>4.916592502868027</v>
+        <v>5.223879534297279</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.178940124080178</v>
+        <v>6.13101441302133</v>
       </c>
       <c r="C2" t="n">
-        <v>6.684720118216532</v>
+        <v>5.073672135547516</v>
       </c>
       <c r="D2" t="n">
-        <v>11.25082869066845</v>
+        <v>17.89431540530661</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.43231314723387</v>
+        <v>12.15894531709675</v>
       </c>
       <c r="C3" t="n">
-        <v>44.08047192068179</v>
+        <v>8.855364292306231</v>
       </c>
       <c r="D3" t="n">
-        <v>9.267698328089891</v>
+        <v>13.70028921276424</v>
       </c>
     </row>
     <row r="4">
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
-        <v>18.43525839034661</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4585,10 +4585,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>20.72076704583318</v>
+        <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
       </c>
       <c r="D9" t="n">
-        <v>39.60468413702056</v>
+        <v>39.2718716652809</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>50.67781649322036</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>26.15866757965626</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39625898792774</v>
+        <v>13.39825718402039</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13335587797465</v>
+        <v>70.14381702222443</v>
       </c>
       <c r="D21" t="n">
-        <v>1.57603046916797</v>
+        <v>1.576265551061223</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.612651625179015</v>
+        <v>4.596542751283566</v>
       </c>
       <c r="C2" t="n">
-        <v>4.962734644967626</v>
+        <v>4.557272843113694</v>
       </c>
       <c r="D2" t="n">
-        <v>12.50648400440012</v>
+        <v>25.06205539401257</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.3767954964483</v>
+        <v>17.58310138306037</v>
       </c>
       <c r="C3" t="n">
-        <v>32.8100082759284</v>
+        <v>15.89449533175586</v>
       </c>
       <c r="D3" t="n">
-        <v>16.47863521578271</v>
+        <v>25.41744806294992</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.24992905842221</v>
+        <v>14.15385665212627</v>
       </c>
       <c r="C4" t="n">
-        <v>67.69346770322606</v>
+        <v>14.0517548908846</v>
       </c>
       <c r="D4" t="n">
-        <v>19.92260616228052</v>
+        <v>22.24542123052848</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.117048960983624</v>
+        <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.424156065963628</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.58368222013712</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3139636433765</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>25.20146356801562</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.96770980341364</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>40.04843409934012</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68134257340984</v>
+        <v>50.1084028247572</v>
       </c>
     </row>
     <row r="11">
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4980,7 +4980,7 @@
         <v>5.203262832508096</v>
       </c>
       <c r="C13" t="n">
-        <v>26.53664044579129</v>
+        <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
         <v>44.74806035956962</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43380450622641</v>
+        <v>15.44236237309554</v>
       </c>
       <c r="C21" t="n">
-        <v>86.10438303473678</v>
+        <v>86.15212692358567</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249222001310822</v>
+        <v>3.251023657493799</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.943500601510189</v>
+        <v>6.273367830137119</v>
       </c>
       <c r="C2" t="n">
-        <v>5.729479601984385</v>
+        <v>7.028331814702915</v>
       </c>
       <c r="D2" t="n">
-        <v>15.64022267635594</v>
+        <v>21.8978825432251</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.57390580082366</v>
+        <v>16.64553232550467</v>
       </c>
       <c r="C3" t="n">
-        <v>24.74004214701962</v>
+        <v>17.00877897607599</v>
       </c>
       <c r="D3" t="n">
-        <v>22.65873701401638</v>
+        <v>39.56934121966769</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.50588747179015</v>
+        <v>25.34676222824415</v>
       </c>
       <c r="C4" t="n">
-        <v>76.0913375653533</v>
+        <v>29.20110371511713</v>
       </c>
       <c r="D4" t="n">
-        <v>23.71313404837746</v>
+        <v>29.97962964458485</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>17.94143929511046</v>
+        <v>12.64000169217769</v>
       </c>
       <c r="C5" t="n">
-        <v>72.40389318820228</v>
+        <v>17.05786636128833</v>
       </c>
       <c r="D5" t="n">
-        <v>30.11511082777092</v>
+        <v>30.43417883165113</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.31700669748049</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
-        <v>36.10573531908495</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.43373686329462</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.45733986592554</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.13598957146735</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.50937249425062</v>
       </c>
       <c r="D9" t="n">
-        <v>41.04687151455913</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>29.60951076008381</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>49.39663573917827</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5263,10 +5263,10 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
-        <v>49.04418831335365</v>
+        <v>49.75497365122833</v>
       </c>
     </row>
     <row r="12">
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5291,10 +5291,10 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>45.52854978444583</v>
       </c>
     </row>
     <row r="14">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5347,10 +5347,10 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.71733827665514</v>
+        <v>16.73823126245033</v>
       </c>
       <c r="C21" t="n">
-        <v>101.1398965737636</v>
+        <v>102.103210700947</v>
       </c>
       <c r="D21" t="n">
-        <v>4.179334569163784</v>
+        <v>5.0214693787351</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.08192702780899</v>
+        <v>5.947427592327178</v>
       </c>
       <c r="C2" t="n">
-        <v>4.797801030654163</v>
+        <v>4.233296100712247</v>
       </c>
       <c r="D2" t="n">
-        <v>27.49678970054466</v>
+        <v>27.38781570537327</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.04376204053038</v>
+        <v>19.30606860401353</v>
       </c>
       <c r="C3" t="n">
-        <v>23.29196428325558</v>
+        <v>23.04161861867264</v>
       </c>
       <c r="D3" t="n">
-        <v>29.50151851261665</v>
+        <v>47.40859663807848</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.44131310748811</v>
+        <v>28.98413747247858</v>
       </c>
       <c r="C4" t="n">
-        <v>68.29331555052087</v>
+        <v>36.80768492762142</v>
       </c>
       <c r="D4" t="n">
-        <v>29.40530723760046</v>
+        <v>42.06592563156733</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.02384934900497</v>
+        <v>25.62361508084176</v>
       </c>
       <c r="C5" t="n">
-        <v>108.5076650118787</v>
+        <v>37.33095645398497</v>
       </c>
       <c r="D5" t="n">
-        <v>31.857713002809</v>
+        <v>34.45934441906305</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.89311267342412</v>
+        <v>11.5119735799981</v>
       </c>
       <c r="C6" t="n">
-        <v>64.16113946334606</v>
+        <v>20.0855762811855</v>
       </c>
       <c r="D6" t="n">
-        <v>37.39378830705677</v>
+        <v>38.40007970390975</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.37951975538279</v>
+        <v>21.02020009562846</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>31.87734795689393</v>
       </c>
       <c r="D8" t="n">
-        <v>39.55461500410399</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>33.39218466454675</v>
+        <v>34.27968458918587</v>
       </c>
       <c r="D9" t="n">
-        <v>42.04530892977813</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5563,7 +5563,7 @@
         <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>48.82722207071512</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>9.062513057902304</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>50.28806265463436</v>
+        <v>50.46575898910303</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
         <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
-        <v>47.51560713784138</v>
+        <v>47.29864089520282</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.780555844801</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>45.26838664282043</v>
+        <v>46.30903920932205</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.77765165941727</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.0278172139468</v>
+        <v>18.06884562033058</v>
       </c>
       <c r="C21" t="n">
-        <v>116.751578147465</v>
+        <v>117.8777071421567</v>
       </c>
       <c r="D21" t="n">
-        <v>6.009272404648932</v>
+        <v>6.883369760125936</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.470699118690727</v>
+        <v>7.113743864972388</v>
       </c>
       <c r="C2" t="n">
-        <v>4.047745784609599</v>
+        <v>5.703954161673968</v>
       </c>
       <c r="D2" t="n">
-        <v>34.64391298746145</v>
+        <v>34.02835717689869</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.52557917913731</v>
+        <v>17.81381209355838</v>
       </c>
       <c r="C3" t="n">
-        <v>19.38951715887451</v>
+        <v>18.05924901962008</v>
       </c>
       <c r="D3" t="n">
-        <v>40.40873550679871</v>
+        <v>54.26119561372121</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.77993394999525</v>
+        <v>24.72138894063893</v>
       </c>
       <c r="C4" t="n">
-        <v>51.91874559138832</v>
+        <v>40.8151790563569</v>
       </c>
       <c r="D4" t="n">
-        <v>31.702596865538</v>
+        <v>48.15374314560181</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.05344064885261</v>
+        <v>21.23029410433728</v>
       </c>
       <c r="C5" t="n">
-        <v>87.42463306317848</v>
+        <v>40.22711218151306</v>
       </c>
       <c r="D5" t="n">
-        <v>28.47068342315751</v>
+        <v>33.94392687433348</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.70443718775948</v>
+        <v>12.80002656796992</v>
       </c>
       <c r="C6" t="n">
-        <v>80.26180181299375</v>
+        <v>27.33087433852696</v>
       </c>
       <c r="D6" t="n">
-        <v>29.98748362621883</v>
+        <v>31.27553661419064</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.527640485537042</v>
+        <v>5.629341336151211</v>
       </c>
       <c r="C7" t="n">
-        <v>35.63253292563798</v>
+        <v>16.28915790886308</v>
       </c>
       <c r="D7" t="n">
-        <v>31.02126395879071</v>
+        <v>31.20092378866788</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
-        <v>29.45733986592554</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.52187317249857</v>
+        <v>22.2984356065578</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.06830573313655</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.29539255245382</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.32797015314322</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>29.80684204863741</v>
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
         <v>27.95035713990669</v>
@@ -5969,10 +5969,10 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.038683204421661</v>
+        <v>7.064354058885095</v>
       </c>
       <c r="C21" t="n">
-        <v>65.98765504145307</v>
+        <v>66.22831930204777</v>
       </c>
       <c r="D21" t="n">
-        <v>4.399177002763538</v>
+        <v>5.298265544163821</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.478152189697202</v>
+        <v>6.366633862040565</v>
       </c>
       <c r="C2" t="n">
-        <v>6.508987279156353</v>
+        <v>8.396888114422969</v>
       </c>
       <c r="D2" t="n">
-        <v>25.09641656366122</v>
+        <v>24.65168485363741</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.930861054542</v>
+        <v>22.21204180858409</v>
       </c>
       <c r="C3" t="n">
-        <v>17.10695374650067</v>
+        <v>20.84250376115979</v>
       </c>
       <c r="D3" t="n">
-        <v>59.74425654193965</v>
+        <v>70.57293371978197</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.18307240354219</v>
+        <v>31.01340997715674</v>
       </c>
       <c r="C4" t="n">
-        <v>49.940523967331</v>
+        <v>43.73784197189966</v>
       </c>
       <c r="D4" t="n">
-        <v>45.52462279362884</v>
+        <v>66.31509392646355</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.03643214271093</v>
+        <v>30.85142160595602</v>
       </c>
       <c r="C5" t="n">
-        <v>92.75061435871743</v>
+        <v>62.14462967882311</v>
       </c>
       <c r="D5" t="n">
-        <v>33.55122779263475</v>
+        <v>44.71860792844222</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.57867567062465</v>
+        <v>22.21891404251382</v>
       </c>
       <c r="C6" t="n">
-        <v>114.435457650121</v>
+        <v>49.22777513404782</v>
       </c>
       <c r="D6" t="n">
-        <v>32.76484788153306</v>
+        <v>35.17994723398021</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.07335334037803</v>
+        <v>11.19879606234337</v>
       </c>
       <c r="C7" t="n">
-        <v>81.56556276423349</v>
+        <v>30.12296480940488</v>
       </c>
       <c r="D7" t="n">
-        <v>33.17718191731671</v>
+        <v>33.83593462686632</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.258641614573416</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>35.04839304161113</v>
+        <v>20.77869016038374</v>
       </c>
       <c r="D8" t="n">
-        <v>31.29320807286708</v>
+        <v>32.46148784092078</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>22.96406055003713</v>
+        <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.20008090968388</v>
+        <v>25.0542014123786</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.909319358310797</v>
+        <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>34.82848155585983</v>
+        <v>35.18387422479719</v>
       </c>
     </row>
     <row r="12">
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
         <v>32.97886888105885</v>
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
-        <v>30.69925071179776</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6294,7 +6294,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.253936640418012</v>
+        <v>7.289467882080277</v>
       </c>
       <c r="C21" t="n">
-        <v>75.25959264433689</v>
+        <v>76.53941276184291</v>
       </c>
       <c r="D21" t="n">
-        <v>5.440452480313509</v>
+        <v>6.378284396820242</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.394703634836223</v>
+        <v>5.529203070318036</v>
       </c>
       <c r="C2" t="n">
-        <v>4.75264063625881</v>
+        <v>6.024985660962675</v>
       </c>
       <c r="D2" t="n">
-        <v>24.41606540461818</v>
+        <v>24.13626730890783</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.78712497909446</v>
+        <v>22.19240685449915</v>
       </c>
       <c r="C3" t="n">
-        <v>21.89788254322511</v>
+        <v>28.15161541927729</v>
       </c>
       <c r="D3" t="n">
-        <v>65.52675051995337</v>
+        <v>73.92069339126358</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.52239725631309</v>
+        <v>38.33921134624644</v>
       </c>
       <c r="C4" t="n">
-        <v>45.42252103238718</v>
+        <v>48.84293003398307</v>
       </c>
       <c r="D4" t="n">
-        <v>63.72426173495622</v>
+        <v>86.14836104765762</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.81049130201392</v>
+        <v>39.49080140332795</v>
       </c>
       <c r="C5" t="n">
-        <v>92.57880851047423</v>
+        <v>73.06657288856887</v>
       </c>
       <c r="D5" t="n">
-        <v>42.36241343824987</v>
+        <v>59.24847395129502</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.29190752999335</v>
+        <v>33.24786775202249</v>
       </c>
       <c r="C6" t="n">
-        <v>132.669457761097</v>
+        <v>76.96116603131597</v>
       </c>
       <c r="D6" t="n">
-        <v>35.82397372796611</v>
+        <v>41.62021217383928</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.43373686329462</v>
+        <v>19.52303484665207</v>
       </c>
       <c r="C7" t="n">
-        <v>126.7200666733613</v>
+        <v>52.58044354405067</v>
       </c>
       <c r="D7" t="n">
-        <v>35.57264631567892</v>
+        <v>36.4110588551057</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.01520924164921</v>
+        <v>9.429686699290613</v>
       </c>
       <c r="C8" t="n">
-        <v>73.18438261307848</v>
+        <v>31.71045084717197</v>
       </c>
       <c r="D8" t="n">
-        <v>33.37942194439155</v>
+        <v>34.71459882216722</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>25.4046853427947</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.47773558353648</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>25.76596849795753</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>33.84673385161303</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.456323333545995</v>
+        <v>7.502976808746247</v>
       </c>
       <c r="C21" t="n">
-        <v>83.88363750239243</v>
+        <v>86.28423330058183</v>
       </c>
       <c r="D21" t="n">
-        <v>6.524282916852745</v>
+        <v>7.502976808746247</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_7_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_7_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497646374604</v>
+        <v>10.84497635135687</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907240022618</v>
+        <v>37.78907200860871</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.065638227464294</v>
+        <v>1.082867717784232</v>
       </c>
       <c r="C2" t="n">
-        <v>4.548437113775472</v>
+        <v>3.579452129683871</v>
       </c>
       <c r="D2" t="n">
-        <v>33.53257458625406</v>
+        <v>13.47056024997049</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.38108234016379</v>
+        <v>10.77468105410875</v>
       </c>
       <c r="C3" t="n">
-        <v>25.65306751196916</v>
+        <v>33.26161221988194</v>
       </c>
       <c r="D3" t="n">
-        <v>75.82037519898117</v>
+        <v>61.48685871697774</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.57268737340794</v>
+        <v>20.35653864755761</v>
       </c>
       <c r="C4" t="n">
-        <v>60.21451369227387</v>
+        <v>101.0041673083203</v>
       </c>
       <c r="D4" t="n">
-        <v>102.8675244509808</v>
+        <v>70.53955429783758</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.06284151973436</v>
+        <v>18.45685683984004</v>
       </c>
       <c r="C5" t="n">
-        <v>82.34408869370124</v>
+        <v>125.7373372214103</v>
       </c>
       <c r="D5" t="n">
-        <v>75.25096153051803</v>
+        <v>45.03767593232243</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.51203999992289</v>
+        <v>11.79373517111693</v>
       </c>
       <c r="C6" t="n">
-        <v>96.76498072138264</v>
+        <v>88.110874708447</v>
       </c>
       <c r="D6" t="n">
-        <v>50.636583089642</v>
+        <v>29.82647700272235</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.00319158948677</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>83.48193428292328</v>
+        <v>49.52622643613884</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>28.86534600026472</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.35453409442011</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>51.57120690408495</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>36.96770980341364</v>
+        <v>30.95941385342316</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.765624340592267</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>32.8374972116473</v>
+        <v>31.50624732468863</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>34.94530953266521</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>29.60951076008381</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>38.43542262126263</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>31.09685853201771</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>37.49392657288993</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>37.5351599764683</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>26.27647730416588</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.9443845382232</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>84.85539932116455</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.703134289529348</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>95.32628683292567</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.666026075720515</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.318348298083224</v>
+        <v>1.440223882130071</v>
       </c>
       <c r="C2" t="n">
-        <v>10.21606661039231</v>
+        <v>6.958627727701391</v>
       </c>
       <c r="D2" t="n">
-        <v>25.22698900832604</v>
+        <v>20.2534551386117</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.22185928562655</v>
+        <v>6.99004365423729</v>
       </c>
       <c r="C3" t="n">
-        <v>21.34319509032566</v>
+        <v>21.88806506618264</v>
       </c>
       <c r="D3" t="n">
-        <v>83.21293541195965</v>
+        <v>58.04583301359267</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.34746623850791</v>
+        <v>20.85428473361074</v>
       </c>
       <c r="C4" t="n">
-        <v>62.12892171555515</v>
+        <v>91.91711055781187</v>
       </c>
       <c r="D4" t="n">
-        <v>114.1242436278747</v>
+        <v>84.68064822980863</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.43791020048565</v>
+        <v>24.56823629877644</v>
       </c>
       <c r="C5" t="n">
-        <v>95.57313900842701</v>
+        <v>158.6258853136784</v>
       </c>
       <c r="D5" t="n">
-        <v>92.94696389956678</v>
+        <v>59.32210502911353</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.66174867705392</v>
+        <v>18.15349679922777</v>
       </c>
       <c r="C6" t="n">
-        <v>113.429166253268</v>
+        <v>146.9587955964093</v>
       </c>
       <c r="D6" t="n">
-        <v>60.61899374642356</v>
+        <v>36.58875518957439</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.18391528252619</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
-        <v>109.8919292748667</v>
+        <v>89.11127561907448</v>
       </c>
       <c r="D7" t="n">
-        <v>45.03473068920969</v>
+        <v>30.96137734883166</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23.36559536107409</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>80.02716411167874</v>
+        <v>48.06636759992384</v>
       </c>
       <c r="D8" t="n">
-        <v>38.88702656521616</v>
+        <v>32.29459073119883</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.42656152972862</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>47.48124596819272</v>
+        <v>35.16718451382499</v>
       </c>
       <c r="D9" t="n">
-        <v>36.0546844384641</v>
+        <v>35.27812200440487</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
         <v>34.73423377625215</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>39.14718970684157</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.16303653882975</v>
+        <v>34.29539255245382</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>38.38240824523329</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>31.02617269731195</v>
+        <v>28.63954402828795</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>37.96909246174538</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>28.35778243716912</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>26.42668470291564</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>28.88498095434966</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>46.33947338815369</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.888276006803159</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>104.5196570901419</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.860345008503948</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.941758090279949</v>
+        <v>0.7667449570167589</v>
       </c>
       <c r="C2" t="n">
-        <v>6.403940274801944</v>
+        <v>2.944261365036184</v>
       </c>
       <c r="D2" t="n">
-        <v>32.55868086364122</v>
+        <v>13.80042747859741</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.52405765208533</v>
+        <v>6.778967897824225</v>
       </c>
       <c r="C3" t="n">
-        <v>30.06111470403734</v>
+        <v>25.96722677732814</v>
       </c>
       <c r="D3" t="n">
-        <v>83.24729658160828</v>
+        <v>61.7421131200819</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.97283952611313</v>
+        <v>22.59001467471911</v>
       </c>
       <c r="C4" t="n">
-        <v>57.84064774340508</v>
+        <v>85.38259783834509</v>
       </c>
       <c r="D4" t="n">
-        <v>126.3509295365645</v>
+        <v>93.1550944128671</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.18051237552373</v>
+        <v>24.37188675792708</v>
       </c>
       <c r="C5" t="n">
-        <v>102.9853341754904</v>
+        <v>183.0223157642116</v>
       </c>
       <c r="D5" t="n">
-        <v>107.4277425372073</v>
+        <v>66.70975650357077</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>63.31585468998956</v>
+        <v>14.00757624419349</v>
       </c>
       <c r="C6" t="n">
-        <v>129.5298286029157</v>
+        <v>187.3312064381509</v>
       </c>
       <c r="D6" t="n">
-        <v>73.01650375565229</v>
+        <v>37.31328499530853</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>50.783845245279</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="C7" t="n">
-        <v>134.6250991879566</v>
+        <v>85.33841919165398</v>
       </c>
       <c r="D7" t="n">
-        <v>50.30475236560656</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>32.04424506661589</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>108.5665698741335</v>
+        <v>42.80910864368217</v>
       </c>
       <c r="D8" t="n">
-        <v>41.72427743048944</v>
+        <v>35.9663271450819</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.64062358698343</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>70.44530651822986</v>
+        <v>26.5140602485936</v>
       </c>
       <c r="D9" t="n">
-        <v>37.27499683484289</v>
+        <v>40.93593402397924</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.541205026947251</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>44.12955930589413</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>36.01541453029424</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>35.7169632282032</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>37.49392657288993</v>
+        <v>30.38607319414302</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.95941385342317</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>33.82120841130262</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>28.5776939229204</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>22.31905230834699</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>20.30548776693678</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>40.12893741108837</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>19.25796296650543</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.058712812782316</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>112.8219793789524</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.08073011757568</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.166177403924969</v>
+        <v>0.5890486225480862</v>
       </c>
       <c r="C2" t="n">
-        <v>4.30300018771377</v>
+        <v>3.271183350550372</v>
       </c>
       <c r="D2" t="n">
-        <v>26.4257029552114</v>
+        <v>12.42696244035613</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.97628349084461</v>
+        <v>4.614214209960009</v>
       </c>
       <c r="C3" t="n">
-        <v>41.70955121492574</v>
+        <v>17.69109363052752</v>
       </c>
       <c r="D3" t="n">
-        <v>92.48063374004954</v>
+        <v>59.09139431861552</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.99315312826605</v>
+        <v>18.14858806070654</v>
       </c>
       <c r="C4" t="n">
-        <v>84.17013942360029</v>
+        <v>74.98098091185014</v>
       </c>
       <c r="D4" t="n">
-        <v>121.7691130008446</v>
+        <v>101.961371319961</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.66198535676539</v>
+        <v>29.20699420134261</v>
       </c>
       <c r="C5" t="n">
-        <v>77.38626278725484</v>
+        <v>173.3275571847744</v>
       </c>
       <c r="D5" t="n">
-        <v>73.53290304808611</v>
+        <v>83.00676839406783</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.51704654943536</v>
+        <v>22.21891404251382</v>
       </c>
       <c r="C6" t="n">
-        <v>88.67439789068467</v>
+        <v>239.2558425157647</v>
       </c>
       <c r="D6" t="n">
-        <v>33.12711278440013</v>
+        <v>48.22148373719484</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.19985992550562</v>
+        <v>8.92310488389926</v>
       </c>
       <c r="C7" t="n">
-        <v>76.29554108783661</v>
+        <v>172.2338902422434</v>
       </c>
       <c r="D7" t="n">
-        <v>29.34443887993716</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.51590057081509</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>51.90500112352886</v>
+        <v>74.18576527141022</v>
       </c>
       <c r="D8" t="n">
-        <v>27.45457454926205</v>
+        <v>37.1346069131356</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>33.61405964570653</v>
+        <v>38.49530923122167</v>
       </c>
       <c r="D9" t="n">
-        <v>27.40156017323271</v>
+        <v>42.04530892977813</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>27.90126975469435</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>29.32480392585223</v>
+        <v>31.74481201682062</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>28.07602084605028</v>
+        <v>31.45225120095506</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>27.55471281509523</v>
+        <v>30.8092064546734</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
+        <v>21.20280516861837</v>
+      </c>
+      <c r="D14" t="n">
         <v>20.89551813718911</v>
-      </c>
-      <c r="D14" t="n">
-        <v>23.96838845148163</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>37.61173629739955</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>47.6942852200143</v>
       </c>
       <c r="D17" t="n">
-        <v>18.41660518396592</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.58662746324986</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.871432108472673</v>
+        <v>0.3612831551628262</v>
       </c>
       <c r="C2" t="n">
-        <v>2.141191742962294</v>
+        <v>2.048907458763093</v>
       </c>
       <c r="D2" t="n">
-        <v>19.16371518689774</v>
+        <v>9.466011364347745</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.43770491184061</v>
+        <v>3.495021827118645</v>
       </c>
       <c r="C3" t="n">
-        <v>29.13827186204533</v>
+        <v>15.36926030998382</v>
       </c>
       <c r="D3" t="n">
-        <v>92.54444734082558</v>
+        <v>56.09706382066275</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.47509344006</v>
+        <v>14.85580626066273</v>
       </c>
       <c r="C4" t="n">
-        <v>97.30297846330987</v>
+        <v>62.21826075664161</v>
       </c>
       <c r="D4" t="n">
-        <v>138.6286663258751</v>
+        <v>108.7511384425319</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.83441309981433</v>
+        <v>30.40963513904496</v>
       </c>
       <c r="C5" t="n">
-        <v>115.1590057081509</v>
+        <v>164.3445656909161</v>
       </c>
       <c r="D5" t="n">
-        <v>92.75061435871743</v>
+        <v>95.37678946757764</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.99756314516856</v>
+        <v>27.45162930614931</v>
       </c>
       <c r="C6" t="n">
-        <v>106.7473913781642</v>
+        <v>265.0974055869493</v>
       </c>
       <c r="D6" t="n">
-        <v>42.0629803884546</v>
+        <v>58.28439770572465</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.12190094624263</v>
+        <v>9.82140403328509</v>
       </c>
       <c r="C7" t="n">
-        <v>98.7530198224824</v>
+        <v>239.6662130561398</v>
       </c>
       <c r="D7" t="n">
-        <v>32.09922293805371</v>
+        <v>39.04606969330414</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.680032363873551</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>69.26230053461246</v>
+        <v>113.4065860560703</v>
       </c>
       <c r="D8" t="n">
-        <v>28.62285431731576</v>
+        <v>39.8884092235479</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>39.04999668412111</v>
+        <v>50.14374574211007</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>32.59893251951534</v>
       </c>
       <c r="D10" t="n">
-        <v>30.32127784566274</v>
+        <v>32.59893251951534</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>30.03068052520567</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>32.69612554223576</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>23.43235420496287</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.36435157146258</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>14.69185439405351</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>40.5049467818149</v>
       </c>
       <c r="D16" t="n">
-        <v>15.70599977254047</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.851797154387737</v>
+        <v>0.5792311455056182</v>
       </c>
       <c r="C2" t="n">
-        <v>3.182826057168159</v>
+        <v>9.27064357120263</v>
       </c>
       <c r="D2" t="n">
-        <v>19.89609897426586</v>
+        <v>9.333475424274425</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.86981277042945</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C3" t="n">
-        <v>17.96598298771663</v>
+        <v>11.47172192412398</v>
       </c>
       <c r="D3" t="n">
-        <v>86.64414363830225</v>
+        <v>51.13432917569511</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.21755674637784</v>
+        <v>11.01422749394496</v>
       </c>
       <c r="C4" t="n">
-        <v>84.51473286779093</v>
+        <v>50.23406653090079</v>
       </c>
       <c r="D4" t="n">
-        <v>152.0295224888441</v>
+        <v>111.4951232759018</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.03829782712819</v>
+        <v>27.51347941151687</v>
       </c>
       <c r="C5" t="n">
-        <v>147.2866993296277</v>
+        <v>141.8870869562703</v>
       </c>
       <c r="D5" t="n">
-        <v>118.3005983617407</v>
+        <v>109.9311991830366</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.8466360406218</v>
+        <v>33.36862271964485</v>
       </c>
       <c r="C6" t="n">
-        <v>144.5436962439622</v>
+        <v>264.4936307488375</v>
       </c>
       <c r="D6" t="n">
-        <v>58.36490101747288</v>
+        <v>71.60769580005812</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.24273802932299</v>
+        <v>18.50496247734813</v>
       </c>
       <c r="C7" t="n">
-        <v>126.1212005737707</v>
+        <v>307.0985358700362</v>
       </c>
       <c r="D7" t="n">
-        <v>36.23139902522853</v>
+        <v>45.15450390912779</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.43659999094934</v>
+        <v>6.592435834017332</v>
       </c>
       <c r="C8" t="n">
-        <v>97.9686034067892</v>
+        <v>200.8606715503762</v>
       </c>
       <c r="D8" t="n">
-        <v>30.79251674370121</v>
+        <v>41.30703465618455</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.434374453633594</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>59.68436993198057</v>
+        <v>87.08593010521329</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>42.71093387325747</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>38.43542262126263</v>
+        <v>43.41779222031519</v>
       </c>
       <c r="D10" t="n">
-        <v>30.89069151412589</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>31.8076438698924</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>33.22921454564179</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>26.4698816019025</v>
+        <v>26.25291535926396</v>
       </c>
       <c r="D12" t="n">
-        <v>29.07347651356504</v>
+        <v>29.72437524148068</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.51223562190536</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
+        <v>20.58823110575986</v>
+      </c>
+      <c r="D14" t="n">
         <v>16.90078672860884</v>
-      </c>
-      <c r="D14" t="n">
-        <v>19.66637001147211</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>32.6087499965578</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>40.91826256530281</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.11106066376691</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.869648539513427</v>
+        <v>0.3887720908817369</v>
       </c>
       <c r="C2" t="n">
-        <v>1.48047553800419</v>
+        <v>4.89401230567035</v>
       </c>
       <c r="D2" t="n">
-        <v>13.72385115766616</v>
+        <v>6.721044783273664</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.38384765682728</v>
+        <v>3.568652904937156</v>
       </c>
       <c r="C3" t="n">
-        <v>16.6357148484622</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="D3" t="n">
-        <v>86.00109889202059</v>
+        <v>54.8796966673967</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>53.15672944644354</v>
+        <v>18.56975782582842</v>
       </c>
       <c r="C4" t="n">
-        <v>78.60559343592936</v>
+        <v>71.9179280746001</v>
       </c>
       <c r="D4" t="n">
-        <v>161.7291898068026</v>
+        <v>114.3029217100476</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.90361846519713</v>
+        <v>20.56761440397068</v>
       </c>
       <c r="C5" t="n">
-        <v>170.824100538945</v>
+        <v>217.9725340353981</v>
       </c>
       <c r="D5" t="n">
-        <v>128.2653375598458</v>
+        <v>102.2244797046991</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.83655652167208</v>
+        <v>11.47172192412398</v>
       </c>
       <c r="C6" t="n">
-        <v>177.9525706194811</v>
+        <v>267.0697367247811</v>
       </c>
       <c r="D6" t="n">
-        <v>57.19760299712343</v>
+        <v>61.06176196103888</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="C7" t="n">
-        <v>131.3912222501676</v>
+        <v>141.2126262834527</v>
       </c>
       <c r="D7" t="n">
-        <v>36.29128563518759</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.422773407631881</v>
+        <v>2.253110981246429</v>
       </c>
       <c r="C8" t="n">
-        <v>75.60439070404686</v>
+        <v>64.17193868809275</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>31.46010518258904</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>29.28749751309084</v>
+        <v>33.05937219280708</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>26.5140602485936</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>26.1930287493049</v>
+        <v>24.91184799526281</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>26.05067533218912</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>21.14586380177204</v>
+        <v>20.96816746730337</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
+        <v>16.91060420565131</v>
+      </c>
+      <c r="D13" t="n">
         <v>13.78864650614645</v>
-      </c>
-      <c r="D13" t="n">
-        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>34.75877746885832</v>
       </c>
       <c r="D15" t="n">
-        <v>12.90016483380309</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.81278928812512</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.316744655573225</v>
+        <v>0.2336559536107408</v>
       </c>
       <c r="C2" t="n">
-        <v>2.521128104505809</v>
+        <v>3.124902942617597</v>
       </c>
       <c r="D2" t="n">
-        <v>11.22137625954104</v>
+        <v>5.289656630481814</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.26265072084841</v>
+        <v>2.43473430653209</v>
       </c>
       <c r="C3" t="n">
-        <v>10.90230825566083</v>
+        <v>20.37617360164255</v>
       </c>
       <c r="D3" t="n">
-        <v>77.8575016852933</v>
+        <v>47.87983553611694</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.35794666808514</v>
+        <v>12.02248238620644</v>
       </c>
       <c r="C4" t="n">
-        <v>60.40595449460199</v>
+        <v>60.91646330081034</v>
       </c>
       <c r="D4" t="n">
-        <v>166.898091469662</v>
+        <v>110.9463263092278</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>63.71542600561801</v>
+        <v>19.26679869584366</v>
       </c>
       <c r="C5" t="n">
-        <v>159.8285262513808</v>
+        <v>158.6013416210722</v>
       </c>
       <c r="D5" t="n">
-        <v>152.4163310843173</v>
+        <v>107.3295677667826</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.59633143376788</v>
+        <v>11.67298020349458</v>
       </c>
       <c r="C6" t="n">
-        <v>222.148888769264</v>
+        <v>254.2294585009371</v>
       </c>
       <c r="D6" t="n">
-        <v>79.05425213677017</v>
+        <v>64.0403844957237</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.37951975538279</v>
+        <v>3.772856427420492</v>
       </c>
       <c r="C7" t="n">
-        <v>188.7625945909427</v>
+        <v>181.1569951261427</v>
       </c>
       <c r="D7" t="n">
-        <v>42.10028680121597</v>
+        <v>34.19525428662065</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.091744504851458</v>
+        <v>1.168279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>117.0783224699534</v>
+        <v>75.18714792974197</v>
       </c>
       <c r="D8" t="n">
-        <v>34.13045893814036</v>
+        <v>27.03733177495716</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>53.80468293124643</v>
+        <v>31.28437234352885</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>20.96718571959912</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>30.32127784566274</v>
+        <v>18.07888397370501</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>19.78712497909446</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.6997904911455</v>
+        <v>13.50492141961912</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>17.41424077792992</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1301147807751</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>8.065057390387548</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.44249047717483</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>24.38563122578652</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.006111470403733</v>
+        <v>0.1963495408493621</v>
       </c>
       <c r="C2" t="n">
-        <v>2.109775816426395</v>
+        <v>5.321072557017713</v>
       </c>
       <c r="D2" t="n">
-        <v>8.198575078165113</v>
+        <v>10.44972256400305</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.80613803837365</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C3" t="n">
-        <v>10.49979169691964</v>
+        <v>15.59015354343935</v>
       </c>
       <c r="D3" t="n">
-        <v>71.0098114481718</v>
+        <v>41.00269286786803</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.83168884087984</v>
+        <v>8.219191779954297</v>
       </c>
       <c r="C4" t="n">
-        <v>47.33692905566846</v>
+        <v>55.22429011158733</v>
       </c>
       <c r="D4" t="n">
-        <v>168.1998889254933</v>
+        <v>110.1678003797601</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>69.63045592370504</v>
+        <v>19.16862392541898</v>
       </c>
       <c r="C5" t="n">
-        <v>146.2804079327748</v>
+        <v>133.0022702328367</v>
       </c>
       <c r="D5" t="n">
-        <v>170.1123334533661</v>
+        <v>123.4056864238241</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.25672884355649</v>
+        <v>18.8377749490878</v>
       </c>
       <c r="C6" t="n">
-        <v>244.1262928765332</v>
+        <v>256.8860677886289</v>
       </c>
       <c r="D6" t="n">
-        <v>94.3901330248096</v>
+        <v>82.47564288607032</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.78065365579224</v>
+        <v>8.444012004226815</v>
       </c>
       <c r="C7" t="n">
-        <v>237.7498415374501</v>
+        <v>281.3472935876424</v>
       </c>
       <c r="D7" t="n">
-        <v>47.78951474732623</v>
+        <v>44.01665831990574</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.006913291658733</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C8" t="n">
-        <v>152.7943039504523</v>
+        <v>159.2198426747477</v>
       </c>
       <c r="D8" t="n">
-        <v>36.13322425480386</v>
+        <v>29.95803119509142</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>65.12030697039516</v>
+        <v>61.79218225299847</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>23.07499804061703</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>25.90832191507333</v>
+        <v>20.35653864755762</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.16670148773948</v>
+        <v>17.05884810899257</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>18.12502611580461</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.00819813899924</v>
+        <v>13.4519070435898</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>14.10280577150543</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.96750451476862</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>8.585383673638358</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.656429361242622</v>
+        <v>0.5016730768701201</v>
       </c>
       <c r="C2" t="n">
-        <v>3.998658399397259</v>
+        <v>10.33682157801467</v>
       </c>
       <c r="D2" t="n">
-        <v>18.52067044061608</v>
+        <v>8.690430677992765</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.05233572796134</v>
+        <v>1.084831213192726</v>
       </c>
       <c r="C3" t="n">
-        <v>9.321694451823465</v>
+        <v>18.52557917913731</v>
       </c>
       <c r="D3" t="n">
-        <v>62.50787632939441</v>
+        <v>39.80005193016569</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.66729500591412</v>
+        <v>5.48796966673967</v>
       </c>
       <c r="C4" t="n">
-        <v>37.49687181600267</v>
+        <v>46.0606570401476</v>
       </c>
       <c r="D4" t="n">
-        <v>165.609056733986</v>
+        <v>106.1985944114902</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>67.66696051521141</v>
+        <v>16.22338081267855</v>
       </c>
       <c r="C5" t="n">
-        <v>119.8959383811417</v>
+        <v>116.8525204979766</v>
       </c>
       <c r="D5" t="n">
-        <v>187.0229376590174</v>
+        <v>132.904095462412</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>73.78128521726055</v>
+        <v>22.50067563363265</v>
       </c>
       <c r="C6" t="n">
-        <v>240.2621339126177</v>
+        <v>235.5929418312199</v>
       </c>
       <c r="D6" t="n">
-        <v>117.9373517111694</v>
+        <v>100.9109012764169</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.86640986342697</v>
+        <v>14.97165248976386</v>
       </c>
       <c r="C7" t="n">
-        <v>289.1325528823196</v>
+        <v>328.6577154552962</v>
       </c>
       <c r="D7" t="n">
-        <v>59.04819741962866</v>
+        <v>55.87420709179872</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>217.38348541285</v>
+        <v>264.0312275801372</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.884374755077128</v>
+        <v>1.442187377538564</v>
       </c>
       <c r="C9" t="n">
-        <v>113.0453029009074</v>
+        <v>126.3578017704942</v>
       </c>
       <c r="D9" t="n">
-        <v>34.16874709860598</v>
+        <v>25.29374785221481</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>48.25780840225197</v>
+        <v>48.54251523648354</v>
       </c>
       <c r="D10" t="n">
-        <v>27.47420950334699</v>
+        <v>21.35301256736813</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>23.63361248433346</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>18.65811511921063</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>14.97067074205961</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04880964777186</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.98419422574081</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>8.600109889202059</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.724570863463152</v>
+        <v>4.291219215262808</v>
       </c>
       <c r="C2" t="n">
-        <v>3.514656781203581</v>
+        <v>13.91038322147305</v>
       </c>
       <c r="D2" t="n">
-        <v>12.57422459599315</v>
+        <v>12.38376554136927</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.297690538565036</v>
+        <v>0.8050331174823845</v>
       </c>
       <c r="C2" t="n">
-        <v>2.20696883914683</v>
+        <v>19.83228537348981</v>
       </c>
       <c r="D2" t="n">
-        <v>13.63058512576272</v>
+        <v>15.39478575029423</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.68127615348505</v>
+        <v>1.354811831860598</v>
       </c>
       <c r="C3" t="n">
-        <v>12.7430852011236</v>
+        <v>29.32971266437346</v>
       </c>
       <c r="D3" t="n">
-        <v>69.60100349257762</v>
+        <v>38.00345363139403</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>51.20403326269664</v>
+        <v>3.803290606252144</v>
       </c>
       <c r="C4" t="n">
-        <v>57.5726306201457</v>
+        <v>46.08618248045802</v>
       </c>
       <c r="D4" t="n">
-        <v>171.8500268898829</v>
+        <v>101.5274388346839</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.05592822807562</v>
+        <v>12.93452600345173</v>
       </c>
       <c r="C5" t="n">
-        <v>191.3917149429157</v>
+        <v>101.6599747747572</v>
       </c>
       <c r="D5" t="n">
-        <v>171.683129780161</v>
+        <v>139.8008730847458</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.11074186859742</v>
+        <v>22.37992066601029</v>
       </c>
       <c r="C6" t="n">
-        <v>242.2344650504495</v>
+        <v>212.0457231448601</v>
       </c>
       <c r="D6" t="n">
-        <v>91.21025221075418</v>
+        <v>115.441749046974</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.126506585127596</v>
+        <v>20.24167416616073</v>
       </c>
       <c r="C7" t="n">
-        <v>152.8306286155095</v>
+        <v>337.9401399989498</v>
       </c>
       <c r="D7" t="n">
-        <v>35.69241953559704</v>
+        <v>69.10914789274997</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.002765316663493</v>
+        <v>9.846929473595507</v>
       </c>
       <c r="C8" t="n">
-        <v>83.28165775125692</v>
+        <v>343.724597472372</v>
       </c>
       <c r="D8" t="n">
-        <v>25.11801501315464</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>36.83124687252333</v>
+        <v>213.1109194039678</v>
       </c>
       <c r="D9" t="n">
-        <v>20.96718571959912</v>
+        <v>27.73437264497238</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>22.63419332141022</v>
+        <v>91.81795403968295</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>22.49183990429443</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.8811517745239</v>
+        <v>36.96083756948391</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>19.19120412261664</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.28224461720434</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>15.62156946997525</v>
       </c>
     </row>
     <row r="13">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
         <v>9.886199381765381</v>
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.13101441302133</v>
+        <v>5.180682635310418</v>
       </c>
       <c r="C2" t="n">
-        <v>5.073672135547516</v>
+        <v>7.177557465748431</v>
       </c>
       <c r="D2" t="n">
-        <v>17.89431540530661</v>
+        <v>12.0951317163207</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.15894531709675</v>
+        <v>6.921321314940013</v>
       </c>
       <c r="C3" t="n">
-        <v>8.855364292306231</v>
+        <v>27.46439202630452</v>
       </c>
       <c r="D3" t="n">
-        <v>13.70028921276424</v>
+        <v>11.46190444708151</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>8.29576810088555</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.32958949118645</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39825718402039</v>
+        <v>11.67725746513158</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14381702222443</v>
+        <v>59.94325498767542</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576265551061223</v>
+        <v>0.7784838310087717</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.596542751283566</v>
+        <v>3.900483628972577</v>
       </c>
       <c r="C2" t="n">
-        <v>4.557272843113694</v>
+        <v>6.274349577841365</v>
       </c>
       <c r="D2" t="n">
-        <v>25.06205539401257</v>
+        <v>18.1289531066216</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.58310138306037</v>
+        <v>13.90154749213484</v>
       </c>
       <c r="C3" t="n">
-        <v>15.89449533175586</v>
+        <v>27.88654353913065</v>
       </c>
       <c r="D3" t="n">
-        <v>25.41744806294992</v>
+        <v>19.22262004915255</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>14.15385665212627</v>
+        <v>8.653124265231385</v>
       </c>
       <c r="C4" t="n">
-        <v>14.0517548908846</v>
+        <v>45.1545039091278</v>
       </c>
       <c r="D4" t="n">
-        <v>22.24542123052848</v>
+        <v>20.27996232662636</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.424156065963628</v>
+        <v>5.080544369477244</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>13.84656962069702</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44236237309554</v>
+        <v>13.62736468641276</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15212692358567</v>
+        <v>73.7480912441161</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251023657493799</v>
+        <v>1.603219374872089</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.273367830137119</v>
+        <v>2.404300127700438</v>
       </c>
       <c r="C2" t="n">
-        <v>7.028331814702915</v>
+        <v>6.510950774564847</v>
       </c>
       <c r="D2" t="n">
-        <v>21.8978825432251</v>
+        <v>22.96798754085413</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.64553232550467</v>
+        <v>13.79355524466769</v>
       </c>
       <c r="C3" t="n">
-        <v>17.00877897607599</v>
+        <v>25.7316073283089</v>
       </c>
       <c r="D3" t="n">
-        <v>39.56934121966769</v>
+        <v>29.80586030093317</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.34676222824415</v>
+        <v>19.69287719948677</v>
       </c>
       <c r="C4" t="n">
-        <v>29.20110371511713</v>
+        <v>60.48253081553325</v>
       </c>
       <c r="D4" t="n">
-        <v>29.97962964458485</v>
+        <v>25.64030479181395</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.64000169217769</v>
+        <v>8.246680715673209</v>
       </c>
       <c r="C5" t="n">
-        <v>17.05786636128833</v>
+        <v>52.05717201768713</v>
       </c>
       <c r="D5" t="n">
-        <v>30.43417883165113</v>
+        <v>27.21895510024282</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>4.508185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>10.58618549489336</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.886960145291375</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.94224111636546</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.699389580518</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.50937249425062</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.95717262057418</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>41.44055234396211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.52854978444583</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73823126245033</v>
+        <v>14.83546090830455</v>
       </c>
       <c r="C21" t="n">
-        <v>102.103210700947</v>
+        <v>87.36438090446013</v>
       </c>
       <c r="D21" t="n">
-        <v>5.0214693787351</v>
+        <v>2.472576818050759</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.947427592327178</v>
+        <v>3.109194979349649</v>
       </c>
       <c r="C2" t="n">
-        <v>4.233296100712247</v>
+        <v>7.031277057815656</v>
       </c>
       <c r="D2" t="n">
-        <v>27.38781570537327</v>
+        <v>20.94853251321844</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.30606860401353</v>
+        <v>10.70595871481147</v>
       </c>
       <c r="C3" t="n">
-        <v>23.04161861867264</v>
+        <v>25.49107914076843</v>
       </c>
       <c r="D3" t="n">
-        <v>47.40859663807848</v>
+        <v>41.26285600949345</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.98413747247858</v>
+        <v>23.85352397008475</v>
       </c>
       <c r="C4" t="n">
-        <v>36.80768492762142</v>
+        <v>62.85639676440204</v>
       </c>
       <c r="D4" t="n">
-        <v>42.06592563156733</v>
+        <v>34.81670058340888</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.62361508084176</v>
+        <v>19.26679869584366</v>
       </c>
       <c r="C5" t="n">
-        <v>37.33095645398497</v>
+        <v>86.12381735505146</v>
       </c>
       <c r="D5" t="n">
-        <v>34.45934441906305</v>
+        <v>30.13965452037709</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.5119735799981</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>20.0855762811855</v>
+        <v>49.95230493978197</v>
       </c>
       <c r="D6" t="n">
-        <v>38.40007970390975</v>
+        <v>33.81139093426016</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>17.72643654788041</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>25.70215489718149</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>35.21529015133309</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>27.29062268265283</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.062513057902304</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>45.4902616239802</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>42.95931604243193</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>46.30903920932205</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06884562033058</v>
+        <v>16.07357406031693</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8777071421567</v>
+        <v>100.6713322725113</v>
       </c>
       <c r="D21" t="n">
-        <v>6.883369760125936</v>
+        <v>3.383910328487775</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.113743864972388</v>
+        <v>2.688025214227767</v>
       </c>
       <c r="C2" t="n">
-        <v>5.703954161673968</v>
+        <v>5.16497467204247</v>
       </c>
       <c r="D2" t="n">
-        <v>34.02835717689869</v>
+        <v>22.97682327019235</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.81381209355838</v>
+        <v>10.64214511403542</v>
       </c>
       <c r="C3" t="n">
-        <v>18.05924901962008</v>
+        <v>26.51700549170635</v>
       </c>
       <c r="D3" t="n">
-        <v>54.26119561372121</v>
+        <v>48.00255399914779</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.72138894063893</v>
+        <v>22.07950586851077</v>
       </c>
       <c r="C4" t="n">
-        <v>40.8151790563569</v>
+        <v>63.37966829076559</v>
       </c>
       <c r="D4" t="n">
-        <v>48.15374314560181</v>
+        <v>46.96681017116741</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.23029410433728</v>
+        <v>27.7343726449724</v>
       </c>
       <c r="C5" t="n">
-        <v>40.22711218151306</v>
+        <v>102.34719816773</v>
       </c>
       <c r="D5" t="n">
-        <v>33.94392687433348</v>
+        <v>35.29382996767284</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.80002656796992</v>
+        <v>16.86544381125596</v>
       </c>
       <c r="C6" t="n">
-        <v>27.33087433852696</v>
+        <v>94.95365620704727</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.02523200733671</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.629341336151211</v>
+        <v>8.144578954431539</v>
       </c>
       <c r="C7" t="n">
-        <v>16.28915790886308</v>
+        <v>45.39405034896402</v>
       </c>
       <c r="D7" t="n">
-        <v>31.20092378866788</v>
+        <v>37.18958478457343</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>22.2984356065578</v>
+        <v>30.39687241888974</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>38.49530923122167</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>6.930157044278233</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>46.37874329632356</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>41.88626580169016</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.064354058885095</v>
+        <v>17.3360184474703</v>
       </c>
       <c r="C21" t="n">
-        <v>66.22831930204777</v>
+        <v>114.417721753304</v>
       </c>
       <c r="D21" t="n">
-        <v>5.298265544163821</v>
+        <v>4.334004611867575</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.366633862040565</v>
+        <v>2.104867077905161</v>
       </c>
       <c r="C2" t="n">
-        <v>8.396888114422969</v>
+        <v>10.82867717784232</v>
       </c>
       <c r="D2" t="n">
-        <v>24.65168485363741</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.21204180858409</v>
+        <v>9.896016858807849</v>
       </c>
       <c r="C3" t="n">
-        <v>20.84250376115979</v>
+        <v>22.95817006381166</v>
       </c>
       <c r="D3" t="n">
-        <v>70.57293371978197</v>
+        <v>54.32991795301848</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.01340997715674</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="C4" t="n">
-        <v>43.73784197189966</v>
+        <v>64.83461838845936</v>
       </c>
       <c r="D4" t="n">
-        <v>66.31509392646355</v>
+        <v>58.98929255737384</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.85142160595602</v>
+        <v>30.31146036862028</v>
       </c>
       <c r="C5" t="n">
-        <v>62.14462967882311</v>
+        <v>108.6058397823034</v>
       </c>
       <c r="D5" t="n">
-        <v>44.71860792844222</v>
+        <v>42.85328729037328</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.21891404251382</v>
+        <v>26.72709950041517</v>
       </c>
       <c r="C6" t="n">
-        <v>49.22777513404782</v>
+        <v>128.2417756149439</v>
       </c>
       <c r="D6" t="n">
-        <v>35.17994723398021</v>
+        <v>39.08435785376978</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.19879606234337</v>
+        <v>13.65414707066464</v>
       </c>
       <c r="C7" t="n">
-        <v>30.12296480940488</v>
+        <v>89.53048188878788</v>
       </c>
       <c r="D7" t="n">
-        <v>33.83593462686632</v>
+        <v>39.34550274309942</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.841398840268521</v>
+        <v>8.428304040958867</v>
       </c>
       <c r="C8" t="n">
-        <v>20.77869016038374</v>
+        <v>41.55738032076748</v>
       </c>
       <c r="D8" t="n">
-        <v>32.46148784092078</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>31.50624732468863</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>39.49374664644068</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>25.0542014123786</v>
+        <v>34.02246669067321</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>43.84485247166256</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>47.08952863419825</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>45.12897846881738</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.289467882080277</v>
+        <v>17.72993040900733</v>
       </c>
       <c r="C21" t="n">
-        <v>76.53941276184291</v>
+        <v>127.6554989448528</v>
       </c>
       <c r="D21" t="n">
-        <v>6.378284396820242</v>
+        <v>5.318979122702198</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.529203070318036</v>
+        <v>2.00374706436774</v>
       </c>
       <c r="C2" t="n">
-        <v>6.024985660962675</v>
+        <v>6.756387700626549</v>
       </c>
       <c r="D2" t="n">
-        <v>24.13626730890783</v>
+        <v>18.71898347687393</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.19240685449915</v>
+        <v>13.72483290537041</v>
       </c>
       <c r="C3" t="n">
-        <v>28.15161541927729</v>
+        <v>40.18293353482196</v>
       </c>
       <c r="D3" t="n">
-        <v>73.92069339126358</v>
+        <v>59.31719629059228</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.33921134624644</v>
+        <v>14.56226369709294</v>
       </c>
       <c r="C4" t="n">
-        <v>48.84293003398307</v>
+        <v>94.04848482373168</v>
       </c>
       <c r="D4" t="n">
-        <v>86.14836104765762</v>
+        <v>54.95627298832795</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.49080140332795</v>
+        <v>15.04528356758237</v>
       </c>
       <c r="C5" t="n">
-        <v>73.06657288856887</v>
+        <v>76.62540831646356</v>
       </c>
       <c r="D5" t="n">
-        <v>59.24847395129502</v>
+        <v>36.10377182367646</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.24786775202249</v>
+        <v>8.45284773356504</v>
       </c>
       <c r="C6" t="n">
-        <v>76.96116603131597</v>
+        <v>58.96867585558468</v>
       </c>
       <c r="D6" t="n">
-        <v>41.62021217383928</v>
+        <v>25.88181472705867</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.52303484665207</v>
+        <v>5.569454726192155</v>
       </c>
       <c r="C7" t="n">
-        <v>52.58044354405067</v>
+        <v>29.22466566001905</v>
       </c>
       <c r="D7" t="n">
-        <v>36.4110588551057</v>
+        <v>26.70942804173872</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.429686699290613</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>31.71045084717197</v>
+        <v>23.19869825135213</v>
       </c>
       <c r="D8" t="n">
-        <v>34.71459882216722</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>25.4046853427947</v>
+        <v>25.95937279569415</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>26.1930287493049</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>36.86953503298896</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>34.10886048864694</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>96.83959354690535</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.502976808746247</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>86.28423330058183</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.502976808746247</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
